--- a/research/traditional_assets/database/data/israel/israel_semiconductor.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_semiconductor.xlsx
@@ -1400,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1537,22 +1537,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1528248349793369</v>
+        <v>0.1525079878588844</v>
       </c>
       <c r="C2">
-        <v>5906.394234414017</v>
+        <v>5863.781663134914</v>
       </c>
       <c r="D2">
-        <v>5635.394234414017</v>
+        <v>5652.12736256699</v>
       </c>
       <c r="E2">
-        <v>-201.9699432075438</v>
+        <v>-142.6242437754683</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>59.34569943207544</v>
       </c>
       <c r="G2">
         <v>271</v>
@@ -1573,28 +1573,28 @@
         <v>187.31</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.985088681433395</v>
       </c>
       <c r="N2">
-        <v>187.31</v>
+        <v>184.3249113185666</v>
       </c>
       <c r="O2">
-        <v>43.08130000000001</v>
+        <v>42.39472960327033</v>
       </c>
       <c r="P2">
-        <v>144.2287</v>
+        <v>141.9301817152963</v>
       </c>
       <c r="Q2">
-        <v>391.2287</v>
+        <v>388.9301817152963</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1528248349793369</v>
+        <v>0.1536572503625095</v>
       </c>
       <c r="T2">
-        <v>1.655640159154051</v>
+        <v>1.668517360391917</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>62.74855456222378</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1619,22 +1619,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1525079878588844</v>
+        <v>0.1521911407384319</v>
       </c>
       <c r="C3">
-        <v>5863.781663134914</v>
+        <v>5821.268758866328</v>
       </c>
       <c r="D3">
-        <v>5652.12736256699</v>
+        <v>5668.960157730479</v>
       </c>
       <c r="E3">
-        <v>-142.6242437754683</v>
+        <v>-83.27854434339288</v>
       </c>
       <c r="F3">
-        <v>59.34569943207544</v>
+        <v>118.6913988641509</v>
       </c>
       <c r="G3">
         <v>271</v>
@@ -1655,28 +1655,28 @@
         <v>187.31</v>
       </c>
       <c r="M3">
-        <v>2.985088681433395</v>
+        <v>5.97017736286679</v>
       </c>
       <c r="N3">
-        <v>184.3249113185666</v>
+        <v>181.3398226371332</v>
       </c>
       <c r="O3">
-        <v>42.39472960327033</v>
+        <v>41.70815920654064</v>
       </c>
       <c r="P3">
-        <v>141.9301817152963</v>
+        <v>139.6316634305926</v>
       </c>
       <c r="Q3">
-        <v>388.9301817152963</v>
+        <v>386.6316634305925</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1536572503625095</v>
+        <v>0.1545066538147264</v>
       </c>
       <c r="T3">
-        <v>1.668517360391917</v>
+        <v>1.681657361655044</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>62.74855456222378</v>
+        <v>31.37427728111189</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1701,22 +1701,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1521911407384319</v>
+        <v>0.1518742936179794</v>
       </c>
       <c r="C4">
-        <v>5821.268758866328</v>
+        <v>5778.856414733375</v>
       </c>
       <c r="D4">
-        <v>5668.960157730479</v>
+        <v>5685.893513029601</v>
       </c>
       <c r="E4">
-        <v>-83.27854434339288</v>
+        <v>-23.93284491131743</v>
       </c>
       <c r="F4">
-        <v>118.6913988641509</v>
+        <v>178.0370982962263</v>
       </c>
       <c r="G4">
         <v>271</v>
@@ -1737,28 +1737,28 @@
         <v>187.31</v>
       </c>
       <c r="M4">
-        <v>5.97017736286679</v>
+        <v>8.955266044300185</v>
       </c>
       <c r="N4">
-        <v>181.3398226371332</v>
+        <v>178.3547339556998</v>
       </c>
       <c r="O4">
-        <v>41.70815920654064</v>
+        <v>41.02158880981096</v>
       </c>
       <c r="P4">
-        <v>139.6316634305926</v>
+        <v>137.3331451458889</v>
       </c>
       <c r="Q4">
-        <v>386.6316634305925</v>
+        <v>384.3331451458889</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1545066538147264</v>
+        <v>0.155373570740185</v>
       </c>
       <c r="T4">
-        <v>1.681657361655044</v>
+        <v>1.695068290779267</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>31.37427728111189</v>
+        <v>20.91618485407459</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1783,22 +1783,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1518742936179794</v>
+        <v>0.1515574464975269</v>
       </c>
       <c r="C5">
-        <v>5778.856414733375</v>
+        <v>5736.545534564311</v>
       </c>
       <c r="D5">
-        <v>5685.893513029601</v>
+        <v>5702.928332292613</v>
       </c>
       <c r="E5">
-        <v>-23.93284491131743</v>
+        <v>35.412854520758</v>
       </c>
       <c r="F5">
-        <v>178.0370982962263</v>
+        <v>237.3827977283018</v>
       </c>
       <c r="G5">
         <v>271</v>
@@ -1819,28 +1819,28 @@
         <v>187.31</v>
       </c>
       <c r="M5">
-        <v>8.955266044300185</v>
+        <v>11.94035472573358</v>
       </c>
       <c r="N5">
-        <v>178.3547339556998</v>
+        <v>175.3696452742664</v>
       </c>
       <c r="O5">
-        <v>41.02158880981096</v>
+        <v>40.33501841308128</v>
       </c>
       <c r="P5">
-        <v>137.3331451458889</v>
+        <v>135.0346268611851</v>
       </c>
       <c r="Q5">
-        <v>384.3331451458889</v>
+        <v>382.0346268611851</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.155373570740185</v>
+        <v>0.1562585484349239</v>
       </c>
       <c r="T5">
-        <v>1.695068290779267</v>
+        <v>1.708758614260244</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>20.91618485407459</v>
+        <v>15.68713864055594</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1865,22 +1865,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1515574464975269</v>
+        <v>0.1512405993770745</v>
       </c>
       <c r="C6">
-        <v>5736.545534564311</v>
+        <v>5694.337033051336</v>
       </c>
       <c r="D6">
-        <v>5702.928332292613</v>
+        <v>5720.065530211714</v>
       </c>
       <c r="E6">
-        <v>35.412854520758</v>
+        <v>94.75855395283347</v>
       </c>
       <c r="F6">
-        <v>237.3827977283018</v>
+        <v>296.7284971603772</v>
       </c>
       <c r="G6">
         <v>271</v>
@@ -1901,28 +1901,28 @@
         <v>187.31</v>
       </c>
       <c r="M6">
-        <v>11.94035472573358</v>
+        <v>14.92544340716697</v>
       </c>
       <c r="N6">
-        <v>175.3696452742664</v>
+        <v>172.384556592833</v>
       </c>
       <c r="O6">
-        <v>40.33501841308128</v>
+        <v>39.6484480163516</v>
       </c>
       <c r="P6">
-        <v>135.0346268611851</v>
+        <v>132.7361085764814</v>
       </c>
       <c r="Q6">
-        <v>382.0346268611851</v>
+        <v>379.7361085764815</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1562585484349239</v>
+        <v>0.1571621572390258</v>
       </c>
       <c r="T6">
-        <v>1.708758614260244</v>
+        <v>1.722737155077663</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>15.68713864055594</v>
+        <v>12.54971091244476</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1947,22 +1947,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1512405993770745</v>
+        <v>0.150923752256622</v>
       </c>
       <c r="C7">
-        <v>5694.337033051336</v>
+        <v>5652.231835914336</v>
       </c>
       <c r="D7">
-        <v>5720.065530211714</v>
+        <v>5737.306032506788</v>
       </c>
       <c r="E7">
-        <v>94.75855395283347</v>
+        <v>154.1042533849089</v>
       </c>
       <c r="F7">
-        <v>296.7284971603772</v>
+        <v>356.0741965924527</v>
       </c>
       <c r="G7">
         <v>271</v>
@@ -1983,28 +1983,28 @@
         <v>187.31</v>
       </c>
       <c r="M7">
-        <v>14.92544340716697</v>
+        <v>17.91053208860037</v>
       </c>
       <c r="N7">
-        <v>172.384556592833</v>
+        <v>169.3994679113996</v>
       </c>
       <c r="O7">
-        <v>39.6484480163516</v>
+        <v>38.96187761962192</v>
       </c>
       <c r="P7">
-        <v>132.7361085764814</v>
+        <v>130.4375902917777</v>
       </c>
       <c r="Q7">
-        <v>379.7361085764815</v>
+        <v>377.4375902917777</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1571621572390258</v>
+        <v>0.1580849917623638</v>
       </c>
       <c r="T7">
-        <v>1.722737155077663</v>
+        <v>1.737013111657155</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>12.54971091244476</v>
+        <v>10.4580924270373</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.150923752256622</v>
+        <v>0.1506069051361695</v>
       </c>
       <c r="C8">
-        <v>5652.231835914336</v>
+        <v>5610.230880067547</v>
       </c>
       <c r="D8">
-        <v>5737.306032506788</v>
+        <v>5754.650776092075</v>
       </c>
       <c r="E8">
-        <v>154.1042533849089</v>
+        <v>213.4499528169843</v>
       </c>
       <c r="F8">
-        <v>356.0741965924527</v>
+        <v>415.419896024528</v>
       </c>
       <c r="G8">
         <v>271</v>
@@ -2065,28 +2065,28 @@
         <v>187.31</v>
       </c>
       <c r="M8">
-        <v>17.91053208860037</v>
+        <v>20.89562077003376</v>
       </c>
       <c r="N8">
-        <v>169.3994679113996</v>
+        <v>166.4143792299662</v>
       </c>
       <c r="O8">
-        <v>38.96187761962192</v>
+        <v>38.27530722289224</v>
       </c>
       <c r="P8">
-        <v>130.4375902917777</v>
+        <v>128.139072007074</v>
       </c>
       <c r="Q8">
-        <v>377.4375902917777</v>
+        <v>375.139072007074</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1580849917623638</v>
+        <v>0.1590276721894296</v>
       </c>
       <c r="T8">
-        <v>1.737013111657155</v>
+        <v>1.75159607805556</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>10.4580924270373</v>
+        <v>8.964079223174828</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2111,22 +2111,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1506069051361695</v>
+        <v>0.150382458015717</v>
       </c>
       <c r="C9">
-        <v>5610.230880067546</v>
+        <v>5563.235385635525</v>
       </c>
       <c r="D9">
-        <v>5754.650776092075</v>
+        <v>5767.000981092128</v>
       </c>
       <c r="E9">
-        <v>213.4499528169844</v>
+        <v>272.7956522490598</v>
       </c>
       <c r="F9">
-        <v>415.4198960245282</v>
+        <v>474.7655954566035</v>
       </c>
       <c r="G9">
         <v>271</v>
@@ -2147,45 +2147,45 @@
         <v>187.31</v>
       </c>
       <c r="M9">
-        <v>20.89562077003377</v>
+        <v>24.59285784465206</v>
       </c>
       <c r="N9">
-        <v>166.4143792299662</v>
+        <v>162.7171421553479</v>
       </c>
       <c r="O9">
-        <v>38.27530722289224</v>
+        <v>37.42494269573003</v>
       </c>
       <c r="P9">
-        <v>128.139072007074</v>
+        <v>125.2921994596179</v>
       </c>
       <c r="Q9">
-        <v>375.139072007074</v>
+        <v>372.2921994596179</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1590276721894296</v>
+        <v>0.1599908456692576</v>
       </c>
       <c r="T9">
-        <v>1.75159607805556</v>
+        <v>1.766496065462627</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.23</v>
       </c>
       <c r="W9">
-        <v>0.038731</v>
+        <v>0.039886</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>8.964079223174824</v>
+        <v>7.616438934555638</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2193,22 +2193,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.150382458015717</v>
+        <v>0.1500771608952646</v>
       </c>
       <c r="C10">
-        <v>5563.235385635525</v>
+        <v>5520.774004668373</v>
       </c>
       <c r="D10">
-        <v>5767.000981092128</v>
+        <v>5783.885299557052</v>
       </c>
       <c r="E10">
-        <v>272.7956522490598</v>
+        <v>332.1413516811352</v>
       </c>
       <c r="F10">
-        <v>474.7655954566035</v>
+        <v>534.111294888679</v>
       </c>
       <c r="G10">
         <v>271</v>
@@ -2229,28 +2229,28 @@
         <v>187.31</v>
       </c>
       <c r="M10">
-        <v>24.59285784465206</v>
+        <v>27.66696507523357</v>
       </c>
       <c r="N10">
-        <v>162.7171421553479</v>
+        <v>159.6430349247664</v>
       </c>
       <c r="O10">
-        <v>37.42494269573003</v>
+        <v>36.71789803269628</v>
       </c>
       <c r="P10">
-        <v>125.2921994596179</v>
+        <v>122.9251368920701</v>
       </c>
       <c r="Q10">
-        <v>372.2921994596179</v>
+        <v>369.9251368920702</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1599908456692576</v>
+        <v>0.160975187796994</v>
       </c>
       <c r="T10">
-        <v>1.766496065462627</v>
+        <v>1.781723525120399</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>7.616438934555638</v>
+        <v>6.770167941827232</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2275,22 +2275,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1500771608952646</v>
+        <v>0.1499027637748121</v>
       </c>
       <c r="C11">
-        <v>5520.774004668373</v>
+        <v>5471.117701604797</v>
       </c>
       <c r="D11">
-        <v>5783.885299557052</v>
+        <v>5793.574695925551</v>
       </c>
       <c r="E11">
-        <v>332.1413516811352</v>
+        <v>391.4870511132106</v>
       </c>
       <c r="F11">
-        <v>534.111294888679</v>
+        <v>593.4569943207543</v>
       </c>
       <c r="G11">
         <v>271</v>
@@ -2311,45 +2311,45 @@
         <v>187.31</v>
       </c>
       <c r="M11">
-        <v>27.66696507523357</v>
+        <v>31.74994919616036</v>
       </c>
       <c r="N11">
-        <v>159.6430349247664</v>
+        <v>155.5600508038397</v>
       </c>
       <c r="O11">
-        <v>36.71789803269628</v>
+        <v>35.77881168488312</v>
       </c>
       <c r="P11">
-        <v>122.9251368920701</v>
+        <v>119.7812391189565</v>
       </c>
       <c r="Q11">
-        <v>369.9251368920702</v>
+        <v>366.7812391189565</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.160975187796994</v>
+        <v>0.1619814041942357</v>
       </c>
       <c r="T11">
-        <v>1.781723525120399</v>
+        <v>1.797289372770565</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.23</v>
       </c>
       <c r="W11">
-        <v>0.039886</v>
+        <v>0.041195</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>6.770167941827232</v>
+        <v>5.899536999027769</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2357,22 +2357,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1499027637748121</v>
+        <v>0.1496783166543596</v>
       </c>
       <c r="C12">
-        <v>5471.117701604797</v>
+        <v>5424.290025177978</v>
       </c>
       <c r="D12">
-        <v>5793.574695925551</v>
+        <v>5806.092718930809</v>
       </c>
       <c r="E12">
-        <v>391.4870511132107</v>
+        <v>450.8327505452861</v>
       </c>
       <c r="F12">
-        <v>593.4569943207545</v>
+        <v>652.8026937528299</v>
       </c>
       <c r="G12">
         <v>271</v>
@@ -2393,45 +2393,45 @@
         <v>187.31</v>
       </c>
       <c r="M12">
-        <v>31.74994919616036</v>
+        <v>35.44718627077867</v>
       </c>
       <c r="N12">
-        <v>155.5600508038396</v>
+        <v>151.8628137292213</v>
       </c>
       <c r="O12">
-        <v>35.77881168488312</v>
+        <v>34.92844715772091</v>
       </c>
       <c r="P12">
-        <v>119.7812391189565</v>
+        <v>116.9343665715004</v>
       </c>
       <c r="Q12">
-        <v>366.7812391189565</v>
+        <v>363.9343665715004</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1619814041942357</v>
+        <v>0.1630102321959097</v>
       </c>
       <c r="T12">
-        <v>1.797289372770565</v>
+        <v>1.813205014749949</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.23</v>
       </c>
       <c r="W12">
-        <v>0.041195</v>
+        <v>0.041811</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>5.899536999027768</v>
+        <v>5.284199388045966</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2439,22 +2439,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1496783166543596</v>
+        <v>0.1493922695339071</v>
       </c>
       <c r="C13">
-        <v>5424.290025177978</v>
+        <v>5380.976565514401</v>
       </c>
       <c r="D13">
-        <v>5806.092718930809</v>
+        <v>5822.124958699306</v>
       </c>
       <c r="E13">
-        <v>450.8327505452861</v>
+        <v>510.1784499773615</v>
       </c>
       <c r="F13">
-        <v>652.8026937528299</v>
+        <v>712.1483931849053</v>
       </c>
       <c r="G13">
         <v>271</v>
@@ -2475,28 +2475,28 @@
         <v>187.31</v>
       </c>
       <c r="M13">
-        <v>35.44718627077867</v>
+        <v>38.66965774994036</v>
       </c>
       <c r="N13">
-        <v>151.8628137292213</v>
+        <v>148.6403422500596</v>
       </c>
       <c r="O13">
-        <v>34.92844715772091</v>
+        <v>34.18727871751371</v>
       </c>
       <c r="P13">
-        <v>116.9343665715004</v>
+        <v>114.4530635325459</v>
       </c>
       <c r="Q13">
-        <v>363.9343665715004</v>
+        <v>361.4530635325459</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1630102321959097</v>
+        <v>0.1640624426521672</v>
       </c>
       <c r="T13">
-        <v>1.813205014749949</v>
+        <v>1.829482375865227</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.284199388045966</v>
+        <v>4.843849439042136</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2521,22 +2521,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1493922695339071</v>
+        <v>0.1491062224134546</v>
       </c>
       <c r="C14">
-        <v>5380.976565514401</v>
+        <v>5337.751889970753</v>
       </c>
       <c r="D14">
-        <v>5822.124958699306</v>
+        <v>5838.245982587734</v>
       </c>
       <c r="E14">
-        <v>510.1784499773615</v>
+        <v>569.524149409437</v>
       </c>
       <c r="F14">
-        <v>712.1483931849053</v>
+        <v>771.4940926169808</v>
       </c>
       <c r="G14">
         <v>271</v>
@@ -2557,28 +2557,28 @@
         <v>187.31</v>
       </c>
       <c r="M14">
-        <v>38.66965774994036</v>
+        <v>41.89212922910205</v>
       </c>
       <c r="N14">
-        <v>148.6403422500596</v>
+        <v>145.4178707708979</v>
       </c>
       <c r="O14">
-        <v>34.18727871751371</v>
+        <v>33.44611027730652</v>
       </c>
       <c r="P14">
-        <v>114.4530635325459</v>
+        <v>111.9717604935914</v>
       </c>
       <c r="Q14">
-        <v>361.4530635325459</v>
+        <v>358.9717604935914</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1640624426521672</v>
+        <v>0.1651388418545456</v>
       </c>
       <c r="T14">
-        <v>1.829482375865227</v>
+        <v>1.846133929190052</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>4.843849439042136</v>
+        <v>4.471245636038895</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2603,22 +2603,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1491062224134546</v>
+        <v>0.1489279752930022</v>
       </c>
       <c r="C15">
-        <v>5337.751889970753</v>
+        <v>5288.49705610578</v>
       </c>
       <c r="D15">
-        <v>5838.245982587734</v>
+        <v>5848.336848154836</v>
       </c>
       <c r="E15">
-        <v>569.524149409437</v>
+        <v>628.8698488415125</v>
       </c>
       <c r="F15">
-        <v>771.4940926169808</v>
+        <v>830.8397920490563</v>
       </c>
       <c r="G15">
         <v>271</v>
@@ -2639,45 +2639,45 @@
         <v>187.31</v>
       </c>
       <c r="M15">
-        <v>41.89212922910205</v>
+        <v>45.94544050031281</v>
       </c>
       <c r="N15">
-        <v>145.4178707708979</v>
+        <v>141.3645594996872</v>
       </c>
       <c r="O15">
-        <v>33.44611027730652</v>
+        <v>32.51384868492805</v>
       </c>
       <c r="P15">
-        <v>111.9717604935914</v>
+        <v>108.8507108147591</v>
       </c>
       <c r="Q15">
-        <v>358.9717604935914</v>
+        <v>355.8507108147591</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1651388418545456</v>
+        <v>0.1662402735965142</v>
       </c>
       <c r="T15">
-        <v>1.846133929190052</v>
+        <v>1.863172727941036</v>
       </c>
       <c r="U15">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V15">
         <v>0.23</v>
       </c>
       <c r="W15">
-        <v>0.041811</v>
+        <v>0.042581</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.471245636038895</v>
+        <v>4.076791907103921</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2685,22 +2685,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1489279752930022</v>
+        <v>0.1486496281725497</v>
       </c>
       <c r="C16">
-        <v>5288.49705610578</v>
+        <v>5244.97900476582</v>
       </c>
       <c r="D16">
-        <v>5848.336848154836</v>
+        <v>5864.164496246952</v>
       </c>
       <c r="E16">
-        <v>628.8698488415125</v>
+        <v>688.215548273588</v>
       </c>
       <c r="F16">
-        <v>830.8397920490563</v>
+        <v>890.1854914811317</v>
       </c>
       <c r="G16">
         <v>271</v>
@@ -2721,28 +2721,28 @@
         <v>187.31</v>
       </c>
       <c r="M16">
-        <v>45.94544050031281</v>
+        <v>49.22725767890659</v>
       </c>
       <c r="N16">
-        <v>141.3645594996872</v>
+        <v>138.0827423210934</v>
       </c>
       <c r="O16">
-        <v>32.51384868492805</v>
+        <v>31.75903073385149</v>
       </c>
       <c r="P16">
-        <v>108.8507108147591</v>
+        <v>106.3237115872419</v>
       </c>
       <c r="Q16">
-        <v>355.8507108147591</v>
+        <v>353.3237115872419</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1662402735965142</v>
+        <v>0.1673676213794703</v>
       </c>
       <c r="T16">
-        <v>1.863172727941036</v>
+        <v>1.880612439603808</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>4.076791907103921</v>
+        <v>3.805005779963659</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2767,22 +2767,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1486496281725497</v>
+        <v>0.1483712810520973</v>
       </c>
       <c r="C17">
-        <v>5244.97900476582</v>
+        <v>5201.546856228765</v>
       </c>
       <c r="D17">
-        <v>5864.164496246952</v>
+        <v>5880.078047141972</v>
       </c>
       <c r="E17">
-        <v>688.2155482735878</v>
+        <v>747.5612477056633</v>
       </c>
       <c r="F17">
-        <v>890.1854914811316</v>
+        <v>949.5311909132071</v>
       </c>
       <c r="G17">
         <v>271</v>
@@ -2803,28 +2803,28 @@
         <v>187.31</v>
       </c>
       <c r="M17">
-        <v>49.22725767890658</v>
+        <v>52.50907485750035</v>
       </c>
       <c r="N17">
-        <v>138.0827423210934</v>
+        <v>134.8009251424996</v>
       </c>
       <c r="O17">
-        <v>31.75903073385149</v>
+        <v>31.00421278277492</v>
       </c>
       <c r="P17">
-        <v>106.3237115872419</v>
+        <v>103.7967123597247</v>
       </c>
       <c r="Q17">
-        <v>353.3237115872419</v>
+        <v>350.7967123597247</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1673676213794703</v>
+        <v>0.1685218107763063</v>
       </c>
       <c r="T17">
-        <v>1.880612439603808</v>
+        <v>1.898467382496646</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.805005779963659</v>
+        <v>3.567192918715931</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2849,22 +2849,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1483712810520973</v>
+        <v>0.1480929339316448</v>
       </c>
       <c r="C18">
-        <v>5201.546856228765</v>
+        <v>5158.201311739469</v>
       </c>
       <c r="D18">
-        <v>5880.078047141972</v>
+        <v>5896.078202084752</v>
       </c>
       <c r="E18">
-        <v>747.5612477056633</v>
+        <v>806.9069471377388</v>
       </c>
       <c r="F18">
-        <v>949.5311909132071</v>
+        <v>1008.876890345283</v>
       </c>
       <c r="G18">
         <v>271</v>
@@ -2885,28 +2885,28 @@
         <v>187.31</v>
       </c>
       <c r="M18">
-        <v>52.50907485750035</v>
+        <v>55.79089203609413</v>
       </c>
       <c r="N18">
-        <v>134.8009251424996</v>
+        <v>131.5191079639059</v>
       </c>
       <c r="O18">
-        <v>31.00421278277492</v>
+        <v>30.24939483169835</v>
       </c>
       <c r="P18">
-        <v>103.7967123597247</v>
+        <v>101.2697131322075</v>
       </c>
       <c r="Q18">
-        <v>350.7967123597247</v>
+        <v>348.2697131322075</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1685218107763063</v>
+        <v>0.1697038119658371</v>
       </c>
       <c r="T18">
-        <v>1.898467382496646</v>
+        <v>1.916752564977263</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.567192918715931</v>
+        <v>3.357358041144406</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2931,22 +2931,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1480929339316448</v>
+        <v>0.1478145868111923</v>
       </c>
       <c r="C19">
-        <v>5158.201311739469</v>
+        <v>5114.943080196181</v>
       </c>
       <c r="D19">
-        <v>5896.078202084752</v>
+        <v>5912.165669973539</v>
       </c>
       <c r="E19">
-        <v>806.9069471377388</v>
+        <v>866.2526465698143</v>
       </c>
       <c r="F19">
-        <v>1008.876890345283</v>
+        <v>1068.222589777358</v>
       </c>
       <c r="G19">
         <v>271</v>
@@ -2967,28 +2967,28 @@
         <v>187.31</v>
       </c>
       <c r="M19">
-        <v>55.79089203609413</v>
+        <v>59.0727092146879</v>
       </c>
       <c r="N19">
-        <v>131.5191079639059</v>
+        <v>128.2372907853121</v>
       </c>
       <c r="O19">
-        <v>30.24939483169835</v>
+        <v>29.49457688062178</v>
       </c>
       <c r="P19">
-        <v>101.2697131322075</v>
+        <v>98.74271390469032</v>
       </c>
       <c r="Q19">
-        <v>348.2697131322075</v>
+        <v>345.7427139046903</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1697038119658371</v>
+        <v>0.1709146424526735</v>
       </c>
       <c r="T19">
-        <v>1.916752564977263</v>
+        <v>1.935483727518382</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.357358041144406</v>
+        <v>3.170838149969716</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3013,22 +3013,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1478145868111923</v>
+        <v>0.1475362396907398</v>
       </c>
       <c r="C20">
-        <v>5114.943080196178</v>
+        <v>5071.772878255239</v>
       </c>
       <c r="D20">
-        <v>5912.165669973536</v>
+        <v>5928.341167464672</v>
       </c>
       <c r="E20">
-        <v>866.2526465698143</v>
+        <v>925.5983460018897</v>
       </c>
       <c r="F20">
-        <v>1068.222589777358</v>
+        <v>1127.568289209433</v>
       </c>
       <c r="G20">
         <v>271</v>
@@ -3049,28 +3049,28 @@
         <v>187.31</v>
       </c>
       <c r="M20">
-        <v>59.0727092146879</v>
+        <v>62.35452639328167</v>
       </c>
       <c r="N20">
-        <v>128.2372907853121</v>
+        <v>124.9554736067183</v>
       </c>
       <c r="O20">
-        <v>29.49457688062178</v>
+        <v>28.73975892954522</v>
       </c>
       <c r="P20">
-        <v>98.74271390469032</v>
+        <v>96.21571467717311</v>
       </c>
       <c r="Q20">
-        <v>345.7427139046903</v>
+        <v>343.2157146771731</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1709146424526735</v>
+        <v>0.1721553699885677</v>
       </c>
       <c r="T20">
-        <v>1.935483727518382</v>
+        <v>1.954677387900024</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.170838149969716</v>
+        <v>3.003951931550258</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1475362396907398</v>
+        <v>0.1476428925702873</v>
       </c>
       <c r="C21">
-        <v>5071.772878255239</v>
+        <v>5006.218845178147</v>
       </c>
       <c r="D21">
-        <v>5928.341167464672</v>
+        <v>5922.132833819655</v>
       </c>
       <c r="E21">
-        <v>925.5983460018897</v>
+        <v>984.9440454339651</v>
       </c>
       <c r="F21">
-        <v>1127.568289209433</v>
+        <v>1186.913988641509</v>
       </c>
       <c r="G21">
         <v>271</v>
@@ -3131,45 +3131,45 @@
         <v>187.31</v>
       </c>
       <c r="M21">
-        <v>62.35452639328167</v>
+        <v>68.60362854347922</v>
       </c>
       <c r="N21">
-        <v>124.9554736067183</v>
+        <v>118.7063714565208</v>
       </c>
       <c r="O21">
-        <v>28.73975892954522</v>
+        <v>27.30246543499978</v>
       </c>
       <c r="P21">
-        <v>96.21571467717311</v>
+        <v>91.40390602152101</v>
       </c>
       <c r="Q21">
-        <v>343.2157146771731</v>
+        <v>338.403906021521</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1721553699885677</v>
+        <v>0.1734271157128592</v>
       </c>
       <c r="T21">
-        <v>1.954677387900024</v>
+        <v>1.974350889791206</v>
       </c>
       <c r="U21">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V21">
         <v>0.23</v>
       </c>
       <c r="W21">
-        <v>0.042581</v>
+        <v>0.044506</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.003951931550258</v>
+        <v>2.730322054048318</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3177,22 +3177,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1476428925702873</v>
+        <v>0.1473837954498349</v>
       </c>
       <c r="C22">
-        <v>5006.218845178147</v>
+        <v>4961.977991527673</v>
       </c>
       <c r="D22">
-        <v>5922.132833819655</v>
+        <v>5937.237679601258</v>
       </c>
       <c r="E22">
-        <v>984.9440454339651</v>
+        <v>1044.289744866041</v>
       </c>
       <c r="F22">
-        <v>1186.913988641509</v>
+        <v>1246.259688073584</v>
       </c>
       <c r="G22">
         <v>271</v>
@@ -3213,28 +3213,28 @@
         <v>187.31</v>
       </c>
       <c r="M22">
-        <v>68.60362854347922</v>
+        <v>72.03380997065318</v>
       </c>
       <c r="N22">
-        <v>118.7063714565208</v>
+        <v>115.2761900293468</v>
       </c>
       <c r="O22">
-        <v>27.30246543499978</v>
+        <v>26.51352370674977</v>
       </c>
       <c r="P22">
-        <v>91.40390602152101</v>
+        <v>88.76266632259706</v>
       </c>
       <c r="Q22">
-        <v>338.403906021521</v>
+        <v>335.7626663225971</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1734271157128592</v>
+        <v>0.1747310575314366</v>
       </c>
       <c r="T22">
-        <v>1.974350889791206</v>
+        <v>1.994522455021406</v>
       </c>
       <c r="U22">
         <v>0.0578</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.730322054048318</v>
+        <v>2.600306718141256</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3259,22 +3259,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1473837954498349</v>
+        <v>0.1477175983293824</v>
       </c>
       <c r="C23">
-        <v>4961.977991527673</v>
+        <v>4883.186513677589</v>
       </c>
       <c r="D23">
-        <v>5937.237679601258</v>
+        <v>5917.791901183248</v>
       </c>
       <c r="E23">
-        <v>1044.289744866041</v>
+        <v>1103.635444298116</v>
       </c>
       <c r="F23">
-        <v>1246.259688073584</v>
+        <v>1305.60538750566</v>
       </c>
       <c r="G23">
         <v>271</v>
@@ -3295,45 +3295,45 @@
         <v>187.31</v>
       </c>
       <c r="M23">
-        <v>72.03380997065318</v>
+        <v>80.03361025409694</v>
       </c>
       <c r="N23">
-        <v>115.2761900293468</v>
+        <v>107.2763897459031</v>
       </c>
       <c r="O23">
-        <v>26.51352370674977</v>
+        <v>24.67356964155771</v>
       </c>
       <c r="P23">
-        <v>88.76266632259706</v>
+        <v>82.60282010434535</v>
       </c>
       <c r="Q23">
-        <v>335.7626663225971</v>
+        <v>329.6028201043454</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1747310575314366</v>
+        <v>0.1760684337556185</v>
       </c>
       <c r="T23">
-        <v>1.994522455021406</v>
+        <v>2.015211239872893</v>
       </c>
       <c r="U23">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V23">
         <v>0.23</v>
       </c>
       <c r="W23">
-        <v>0.044506</v>
+        <v>0.047201</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>2.600306718141256</v>
+        <v>2.340391735488548</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3341,22 +3341,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1477175983293824</v>
+        <v>0.1479813312089299</v>
       </c>
       <c r="C24">
-        <v>4883.186513677589</v>
+        <v>4808.566827498649</v>
       </c>
       <c r="D24">
-        <v>5917.791901183248</v>
+        <v>5902.517914436385</v>
       </c>
       <c r="E24">
-        <v>1103.635444298116</v>
+        <v>1162.981143730191</v>
       </c>
       <c r="F24">
-        <v>1305.60538750566</v>
+        <v>1364.951086937735</v>
       </c>
       <c r="G24">
         <v>271</v>
@@ -3377,45 +3377,45 @@
         <v>187.31</v>
       </c>
       <c r="M24">
-        <v>80.03361025409694</v>
+        <v>87.49336467270884</v>
       </c>
       <c r="N24">
-        <v>107.2763897459031</v>
+        <v>99.81663532729117</v>
       </c>
       <c r="O24">
-        <v>24.67356964155771</v>
+        <v>22.95782612527697</v>
       </c>
       <c r="P24">
-        <v>82.60282010434535</v>
+        <v>76.8588092020142</v>
       </c>
       <c r="Q24">
-        <v>329.6028201043454</v>
+        <v>323.8588092020142</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1760684337556185</v>
+        <v>0.1774405470245843</v>
       </c>
       <c r="T24">
-        <v>2.015211239872893</v>
+        <v>2.036437395759483</v>
       </c>
       <c r="U24">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V24">
         <v>0.23</v>
       </c>
       <c r="W24">
-        <v>0.047201</v>
+        <v>0.04935700000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.340391735488548</v>
+        <v>2.140848059743509</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3423,22 +3423,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1479813312089299</v>
+        <v>0.1477707440884774</v>
       </c>
       <c r="C25">
-        <v>4808.566827498649</v>
+        <v>4761.410842500175</v>
       </c>
       <c r="D25">
-        <v>5902.517914436385</v>
+        <v>5914.707628869985</v>
       </c>
       <c r="E25">
-        <v>1162.981143730191</v>
+        <v>1222.326843162267</v>
       </c>
       <c r="F25">
-        <v>1364.951086937735</v>
+        <v>1424.296786369811</v>
       </c>
       <c r="G25">
         <v>271</v>
@@ -3459,28 +3459,28 @@
         <v>187.31</v>
       </c>
       <c r="M25">
-        <v>87.49336467270884</v>
+        <v>91.29742400630487</v>
       </c>
       <c r="N25">
-        <v>99.81663532729117</v>
+        <v>96.01257599369514</v>
       </c>
       <c r="O25">
-        <v>22.95782612527697</v>
+        <v>22.08289247854988</v>
       </c>
       <c r="P25">
-        <v>76.8588092020142</v>
+        <v>73.92968351514526</v>
       </c>
       <c r="Q25">
-        <v>323.8588092020142</v>
+        <v>320.9296835151453</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1774405470245843</v>
+        <v>0.1788487685374703</v>
       </c>
       <c r="T25">
-        <v>2.036437395759483</v>
+        <v>2.058222134695721</v>
       </c>
       <c r="U25">
         <v>0.0641</v>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.140848059743509</v>
+        <v>2.051646057254196</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3505,22 +3505,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1477707440884774</v>
+        <v>0.149061656968025</v>
       </c>
       <c r="C26">
-        <v>4761.410842500175</v>
+        <v>4628.123154521171</v>
       </c>
       <c r="D26">
-        <v>5914.707628869985</v>
+        <v>5840.765640323058</v>
       </c>
       <c r="E26">
-        <v>1222.326843162267</v>
+        <v>1281.672542594342</v>
       </c>
       <c r="F26">
-        <v>1424.296786369811</v>
+        <v>1483.642485801886</v>
       </c>
       <c r="G26">
         <v>271</v>
@@ -3541,45 +3541,45 @@
         <v>187.31</v>
       </c>
       <c r="M26">
-        <v>91.29742400630487</v>
+        <v>106.6738947291556</v>
       </c>
       <c r="N26">
-        <v>96.01257599369514</v>
+        <v>80.63610527084438</v>
       </c>
       <c r="O26">
-        <v>22.08289247854988</v>
+        <v>18.54630421229421</v>
       </c>
       <c r="P26">
-        <v>73.92968351514526</v>
+        <v>62.08980105855017</v>
       </c>
       <c r="Q26">
-        <v>320.9296835151453</v>
+        <v>309.0898010585502</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1788487685374703</v>
+        <v>0.1802945426240333</v>
       </c>
       <c r="T26">
-        <v>2.058222134695721</v>
+        <v>2.080587800003591</v>
       </c>
       <c r="U26">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V26">
         <v>0.23</v>
       </c>
       <c r="W26">
-        <v>0.04935700000000001</v>
+        <v>0.055363</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.051646057254196</v>
+        <v>1.75591226396654</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3587,22 +3587,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.149061656968025</v>
+        <v>0.1496919098475725</v>
       </c>
       <c r="C27">
-        <v>4628.123154521171</v>
+        <v>4533.344865881942</v>
       </c>
       <c r="D27">
-        <v>5840.765640323058</v>
+        <v>5805.333051115904</v>
       </c>
       <c r="E27">
-        <v>1281.672542594342</v>
+        <v>1341.018242026418</v>
       </c>
       <c r="F27">
-        <v>1483.642485801886</v>
+        <v>1542.988185233962</v>
       </c>
       <c r="G27">
         <v>271</v>
@@ -3623,45 +3623,45 @@
         <v>187.31</v>
       </c>
       <c r="M27">
-        <v>106.6738947291556</v>
+        <v>116.9585044407343</v>
       </c>
       <c r="N27">
-        <v>80.63610527084438</v>
+        <v>70.35149555926571</v>
       </c>
       <c r="O27">
-        <v>18.54630421229421</v>
+        <v>16.18084397863111</v>
       </c>
       <c r="P27">
-        <v>62.08980105855017</v>
+        <v>54.1706515806346</v>
       </c>
       <c r="Q27">
-        <v>309.0898010585502</v>
+        <v>301.1706515806346</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1802945426240333</v>
+        <v>0.1817793916859088</v>
       </c>
       <c r="T27">
-        <v>2.080587800003591</v>
+        <v>2.103557942752215</v>
       </c>
       <c r="U27">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V27">
         <v>0.23</v>
       </c>
       <c r="W27">
-        <v>0.055363</v>
+        <v>0.05836600000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y27">
-        <v>1.75591226396654</v>
+        <v>1.601508166470396</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3669,22 +3669,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1496919098475725</v>
+        <v>0.14957141272712</v>
       </c>
       <c r="C28">
-        <v>4533.344865881942</v>
+        <v>4480.740193651322</v>
       </c>
       <c r="D28">
-        <v>5805.333051115904</v>
+        <v>5812.074078317359</v>
       </c>
       <c r="E28">
-        <v>1341.018242026418</v>
+        <v>1400.363941458493</v>
       </c>
       <c r="F28">
-        <v>1542.988185233962</v>
+        <v>1602.333884666037</v>
       </c>
       <c r="G28">
         <v>271</v>
@@ -3705,28 +3705,28 @@
         <v>187.31</v>
       </c>
       <c r="M28">
-        <v>116.9585044407343</v>
+        <v>121.4569084576856</v>
       </c>
       <c r="N28">
-        <v>70.35149555926571</v>
+        <v>65.85309154231437</v>
       </c>
       <c r="O28">
-        <v>16.18084397863111</v>
+        <v>15.14621105473231</v>
       </c>
       <c r="P28">
-        <v>54.1706515806346</v>
+        <v>50.70688048758207</v>
       </c>
       <c r="Q28">
-        <v>301.1706515806346</v>
+        <v>297.7068804875821</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1817793916859088</v>
+        <v>0.183304921544</v>
       </c>
       <c r="T28">
-        <v>2.103557942752215</v>
+        <v>2.127157404480253</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>1.601508166470396</v>
+        <v>1.542193049193714</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3751,22 +3751,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.14957141272712</v>
+        <v>0.1525124356066676</v>
       </c>
       <c r="C29">
-        <v>4480.740193651322</v>
+        <v>4261.212199205744</v>
       </c>
       <c r="D29">
-        <v>5812.074078317359</v>
+        <v>5651.891783303857</v>
       </c>
       <c r="E29">
-        <v>1400.363941458493</v>
+        <v>1459.709640890569</v>
       </c>
       <c r="F29">
-        <v>1602.333884666037</v>
+        <v>1661.679584098113</v>
       </c>
       <c r="G29">
         <v>271</v>
@@ -3787,45 +3787,45 @@
         <v>187.31</v>
       </c>
       <c r="M29">
-        <v>121.4569084576856</v>
+        <v>149.5511625688301</v>
       </c>
       <c r="N29">
-        <v>65.85309154231437</v>
+        <v>37.75883743116987</v>
       </c>
       <c r="O29">
-        <v>15.14621105473231</v>
+        <v>8.68453260916907</v>
       </c>
       <c r="P29">
-        <v>50.70688048758207</v>
+        <v>29.0743048220008</v>
       </c>
       <c r="Q29">
-        <v>297.7068804875821</v>
+        <v>276.0743048220008</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.183304921544</v>
+        <v>0.1848728272314827</v>
       </c>
       <c r="T29">
-        <v>2.127157404480253</v>
+        <v>2.151412406811848</v>
       </c>
       <c r="U29">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V29">
         <v>0.23</v>
       </c>
       <c r="W29">
-        <v>0.05836600000000001</v>
+        <v>0.0693</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>1.542193049193714</v>
+        <v>1.252481069238038</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3833,22 +3833,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1525124356066676</v>
+        <v>0.1601265780053159</v>
       </c>
       <c r="C30">
-        <v>4261.212199205744</v>
+        <v>3825.450887492991</v>
       </c>
       <c r="D30">
-        <v>5651.891783303857</v>
+        <v>5275.476171023179</v>
       </c>
       <c r="E30">
-        <v>1459.709640890569</v>
+        <v>1519.055340322644</v>
       </c>
       <c r="F30">
-        <v>1661.679584098113</v>
+        <v>1721.025283530188</v>
       </c>
       <c r="G30">
         <v>271</v>
@@ -3869,45 +3869,45 @@
         <v>187.31</v>
       </c>
       <c r="M30">
-        <v>149.5511625688301</v>
+        <v>204.1135986266803</v>
       </c>
       <c r="N30">
-        <v>37.75883743116987</v>
+        <v>-16.80359862668033</v>
       </c>
       <c r="O30">
-        <v>8.68453260916907</v>
+        <v>-3.864827684136475</v>
       </c>
       <c r="P30">
-        <v>29.0743048220008</v>
+        <v>-12.93877094254385</v>
       </c>
       <c r="Q30">
-        <v>276.0743048220008</v>
+        <v>234.0612290574562</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1848728272314827</v>
+        <v>0.1873126172994641</v>
       </c>
       <c r="T30">
-        <v>2.151412406811848</v>
+        <v>2.189155183217297</v>
       </c>
       <c r="U30">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V30">
-        <v>0.23</v>
+        <v>0.2110653101501328</v>
       </c>
       <c r="W30">
-        <v>0.0693</v>
+        <v>0.09356765421619427</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y30">
-        <v>1.252481069238038</v>
+        <v>0.9176752615223165</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3915,22 +3915,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1601265780053158</v>
+        <v>0.1608545780053158</v>
       </c>
       <c r="C31">
-        <v>3825.450887492992</v>
+        <v>3732.724972174788</v>
       </c>
       <c r="D31">
-        <v>5275.47617102318</v>
+        <v>5242.095955137052</v>
       </c>
       <c r="E31">
-        <v>1519.055340322644</v>
+        <v>1578.401039754719</v>
       </c>
       <c r="F31">
-        <v>1721.025283530188</v>
+        <v>1780.370982962263</v>
       </c>
       <c r="G31">
         <v>271</v>
@@ -3951,37 +3951,37 @@
         <v>187.31</v>
       </c>
       <c r="M31">
-        <v>204.1135986266803</v>
+        <v>211.1519985793244</v>
       </c>
       <c r="N31">
-        <v>-16.8035986266803</v>
+        <v>-23.84199857932444</v>
       </c>
       <c r="O31">
-        <v>-3.864827684136469</v>
+        <v>-5.483659673244621</v>
       </c>
       <c r="P31">
-        <v>-12.93877094254383</v>
+        <v>-18.35833890607982</v>
       </c>
       <c r="Q31">
-        <v>234.0612290574562</v>
+        <v>228.6416610939202</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1873126172994641</v>
+        <v>0.1893342261180279</v>
       </c>
       <c r="T31">
-        <v>2.189155183217296</v>
+        <v>2.220428828691829</v>
       </c>
       <c r="U31">
         <v>0.1186</v>
       </c>
       <c r="V31">
-        <v>0.2110653101501328</v>
+        <v>0.2040297998117951</v>
       </c>
       <c r="W31">
-        <v>0.09356765421619426</v>
+        <v>0.09440206574232111</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.9176752615223166</v>
+        <v>0.8870860861382394</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3997,22 +3997,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1608545780053158</v>
+        <v>0.1615825780053158</v>
       </c>
       <c r="C32">
-        <v>3732.724972174788</v>
+        <v>3640.418822897102</v>
       </c>
       <c r="D32">
-        <v>5242.095955137052</v>
+        <v>5209.13550529144</v>
       </c>
       <c r="E32">
-        <v>1578.401039754719</v>
+        <v>1637.746739186795</v>
       </c>
       <c r="F32">
-        <v>1780.370982962263</v>
+        <v>1839.716682394339</v>
       </c>
       <c r="G32">
         <v>271</v>
@@ -4033,37 +4033,37 @@
         <v>187.31</v>
       </c>
       <c r="M32">
-        <v>211.1519985793244</v>
+        <v>218.1903985319686</v>
       </c>
       <c r="N32">
-        <v>-23.84199857932444</v>
+        <v>-30.88039853196858</v>
       </c>
       <c r="O32">
-        <v>-5.483659673244621</v>
+        <v>-7.102491662352774</v>
       </c>
       <c r="P32">
-        <v>-18.35833890607982</v>
+        <v>-23.7779068696158</v>
       </c>
       <c r="Q32">
-        <v>228.6416610939202</v>
+        <v>223.2220931303842</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1893342261180279</v>
+        <v>0.1914144322936514</v>
       </c>
       <c r="T32">
-        <v>2.220428828691829</v>
+        <v>2.252608956643885</v>
       </c>
       <c r="U32">
         <v>0.1186</v>
       </c>
       <c r="V32">
-        <v>0.2040297998117951</v>
+        <v>0.1974481933662533</v>
       </c>
       <c r="W32">
-        <v>0.09440206574232111</v>
+        <v>0.09518264426676237</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.8870860861382394</v>
+        <v>0.8584704059402317</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4079,22 +4079,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1615825780053158</v>
+        <v>0.1623105780053158</v>
       </c>
       <c r="C33">
-        <v>3640.418822897102</v>
+        <v>3548.524571112303</v>
       </c>
       <c r="D33">
-        <v>5209.13550529144</v>
+        <v>5176.586952938717</v>
       </c>
       <c r="E33">
-        <v>1637.746739186795</v>
+        <v>1697.09243861887</v>
       </c>
       <c r="F33">
-        <v>1839.716682394339</v>
+        <v>1899.062381826414</v>
       </c>
       <c r="G33">
         <v>271</v>
@@ -4115,37 +4115,37 @@
         <v>187.31</v>
       </c>
       <c r="M33">
-        <v>218.1903985319686</v>
+        <v>225.2287984846127</v>
       </c>
       <c r="N33">
-        <v>-30.88039853196858</v>
+        <v>-37.91879848461272</v>
       </c>
       <c r="O33">
-        <v>-7.102491662352774</v>
+        <v>-8.721323651460926</v>
       </c>
       <c r="P33">
-        <v>-23.7779068696158</v>
+        <v>-29.19747483315179</v>
       </c>
       <c r="Q33">
-        <v>223.2220931303842</v>
+        <v>217.8025251668482</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1914144322936514</v>
+        <v>0.1935558210038522</v>
       </c>
       <c r="T33">
-        <v>2.252608956643885</v>
+        <v>2.285735558947471</v>
       </c>
       <c r="U33">
         <v>0.1186</v>
       </c>
       <c r="V33">
-        <v>0.1974481933662533</v>
+        <v>0.1912779373235579</v>
       </c>
       <c r="W33">
-        <v>0.09518264426676237</v>
+        <v>0.09591443663342604</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.8584704059402317</v>
+        <v>0.8316432057545995</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1623105780053158</v>
+        <v>0.1630385780053158</v>
       </c>
       <c r="C34">
-        <v>3548.524571112303</v>
+        <v>3457.034543713638</v>
       </c>
       <c r="D34">
-        <v>5176.586952938717</v>
+        <v>5144.442624972127</v>
       </c>
       <c r="E34">
-        <v>1697.09243861887</v>
+        <v>1756.438138050946</v>
       </c>
       <c r="F34">
-        <v>1899.062381826414</v>
+        <v>1958.40808125849</v>
       </c>
       <c r="G34">
         <v>271</v>
@@ -4197,37 +4197,37 @@
         <v>187.31</v>
       </c>
       <c r="M34">
-        <v>225.2287984846127</v>
+        <v>232.2671984372569</v>
       </c>
       <c r="N34">
-        <v>-37.91879848461272</v>
+        <v>-44.95719843725692</v>
       </c>
       <c r="O34">
-        <v>-8.721323651460926</v>
+        <v>-10.34015564056909</v>
       </c>
       <c r="P34">
-        <v>-29.19747483315179</v>
+        <v>-34.61704279668783</v>
       </c>
       <c r="Q34">
-        <v>217.8025251668482</v>
+        <v>212.3829572033122</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1935558210038522</v>
+        <v>0.1957611317651037</v>
       </c>
       <c r="T34">
-        <v>2.285735558947471</v>
+        <v>2.319851015051165</v>
       </c>
       <c r="U34">
         <v>0.1186</v>
       </c>
       <c r="V34">
-        <v>0.1912779373235579</v>
+        <v>0.1854816361925409</v>
       </c>
       <c r="W34">
-        <v>0.09591443663342604</v>
+        <v>0.09660187794756465</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8316432057545995</v>
+        <v>0.8064418964893084</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4243,22 +4243,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1630385780053158</v>
+        <v>0.1943962615933147</v>
       </c>
       <c r="C35">
-        <v>3457.034543713638</v>
+        <v>2312.07738716434</v>
       </c>
       <c r="D35">
-        <v>5144.442624972127</v>
+        <v>4058.831167854905</v>
       </c>
       <c r="E35">
-        <v>1756.438138050946</v>
+        <v>1815.783837483021</v>
       </c>
       <c r="F35">
-        <v>1958.40808125849</v>
+        <v>2017.753780690565</v>
       </c>
       <c r="G35">
         <v>271</v>
@@ -4279,45 +4279,45 @@
         <v>187.31</v>
       </c>
       <c r="M35">
-        <v>232.2671984372569</v>
+        <v>405.1649591626655</v>
       </c>
       <c r="N35">
-        <v>-44.95719843725692</v>
+        <v>-217.8549591626655</v>
       </c>
       <c r="O35">
-        <v>-10.34015564056909</v>
+        <v>-50.10664060741307</v>
       </c>
       <c r="P35">
-        <v>-34.61704279668783</v>
+        <v>-167.7483185552525</v>
       </c>
       <c r="Q35">
-        <v>212.3829572033122</v>
+        <v>79.25168144474753</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1957611317651037</v>
+        <v>0.2020964270766945</v>
       </c>
       <c r="T35">
-        <v>2.319851015051165</v>
+        <v>2.417856018656124</v>
       </c>
       <c r="U35">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.1854816361925409</v>
+        <v>0.1063302712283757</v>
       </c>
       <c r="W35">
-        <v>0.09660187794756465</v>
+        <v>0.1794488815373421</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.8064418964893084</v>
+        <v>0.4623055270798945</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4325,22 +4325,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1943962615933147</v>
+        <v>0.1959462615933147</v>
       </c>
       <c r="C36">
-        <v>2312.07738716434</v>
+        <v>2210.831288458819</v>
       </c>
       <c r="D36">
-        <v>4058.831167854905</v>
+        <v>4016.93076858146</v>
       </c>
       <c r="E36">
-        <v>1815.783837483021</v>
+        <v>1875.129536915097</v>
       </c>
       <c r="F36">
-        <v>2017.753780690565</v>
+        <v>2077.099480122641</v>
       </c>
       <c r="G36">
         <v>271</v>
@@ -4361,37 +4361,37 @@
         <v>187.31</v>
       </c>
       <c r="M36">
-        <v>405.1649591626655</v>
+        <v>417.0815756086263</v>
       </c>
       <c r="N36">
-        <v>-217.8549591626655</v>
+        <v>-229.7715756086263</v>
       </c>
       <c r="O36">
-        <v>-50.10664060741307</v>
+        <v>-52.84746238998405</v>
       </c>
       <c r="P36">
-        <v>-167.7483185552525</v>
+        <v>-176.9241132186422</v>
       </c>
       <c r="Q36">
-        <v>79.25168144474753</v>
+        <v>70.07588678135778</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2020964270766945</v>
+        <v>0.204500987493259</v>
       </c>
       <c r="T36">
-        <v>2.417856018656124</v>
+        <v>2.455053803558525</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.1063302712283757</v>
+        <v>0.1032922634789936</v>
       </c>
       <c r="W36">
-        <v>0.1794488815373421</v>
+        <v>0.1800589134934181</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.4623055270798945</v>
+        <v>0.4490967977347546</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4407,22 +4407,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1959462615933147</v>
+        <v>0.1974962615933147</v>
       </c>
       <c r="C37">
-        <v>2210.831288458819</v>
+        <v>2110.441448413751</v>
       </c>
       <c r="D37">
-        <v>4016.93076858146</v>
+        <v>3975.886627968467</v>
       </c>
       <c r="E37">
-        <v>1875.129536915097</v>
+        <v>1934.475236347172</v>
       </c>
       <c r="F37">
-        <v>2077.099480122641</v>
+        <v>2136.445179554716</v>
       </c>
       <c r="G37">
         <v>271</v>
@@ -4443,37 +4443,37 @@
         <v>187.31</v>
       </c>
       <c r="M37">
-        <v>417.0815756086263</v>
+        <v>428.998192054587</v>
       </c>
       <c r="N37">
-        <v>-229.7715756086263</v>
+        <v>-241.688192054587</v>
       </c>
       <c r="O37">
-        <v>-52.84746238998405</v>
+        <v>-55.58828417255501</v>
       </c>
       <c r="P37">
-        <v>-176.9241132186422</v>
+        <v>-186.099907882032</v>
       </c>
       <c r="Q37">
-        <v>70.07588678135778</v>
+        <v>60.90009211796803</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.204500987493259</v>
+        <v>0.2069806904228412</v>
       </c>
       <c r="T37">
-        <v>2.455053803558525</v>
+        <v>2.493414019239128</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.1032922634789936</v>
+        <v>0.1004230339379104</v>
       </c>
       <c r="W37">
-        <v>0.1800589134934181</v>
+        <v>0.1806350547852676</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.4490967977347546</v>
+        <v>0.4366218866865671</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4489,22 +4489,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1974962615933147</v>
+        <v>0.1990462615933147</v>
       </c>
       <c r="C38">
-        <v>2110.441448413752</v>
+        <v>2010.881885300581</v>
       </c>
       <c r="D38">
-        <v>3975.886627968468</v>
+        <v>3935.672764287372</v>
       </c>
       <c r="E38">
-        <v>1934.475236347172</v>
+        <v>1993.820935779248</v>
       </c>
       <c r="F38">
-        <v>2136.445179554716</v>
+        <v>2195.790878986792</v>
       </c>
       <c r="G38">
         <v>271</v>
@@ -4525,37 +4525,37 @@
         <v>187.31</v>
       </c>
       <c r="M38">
-        <v>428.998192054587</v>
+        <v>440.9148085005477</v>
       </c>
       <c r="N38">
-        <v>-241.688192054587</v>
+        <v>-253.6048085005477</v>
       </c>
       <c r="O38">
-        <v>-55.58828417255501</v>
+        <v>-58.32910595512598</v>
       </c>
       <c r="P38">
-        <v>-186.099907882032</v>
+        <v>-195.2757025454218</v>
       </c>
       <c r="Q38">
-        <v>60.90009211796803</v>
+        <v>51.72429745457825</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2069806904228411</v>
+        <v>0.2095391140803466</v>
       </c>
       <c r="T38">
-        <v>2.493414019239127</v>
+        <v>2.53299201954451</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.1004230339379104</v>
+        <v>0.09770889788553447</v>
       </c>
       <c r="W38">
-        <v>0.1806350547852676</v>
+        <v>0.1811800533045847</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.4366218866865671</v>
+        <v>0.4248212951544976</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4571,22 +4571,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1990462615933147</v>
+        <v>0.2005962615933147</v>
       </c>
       <c r="C39">
-        <v>2010.881885300581</v>
+        <v>1912.127658027747</v>
       </c>
       <c r="D39">
-        <v>3935.672764287372</v>
+        <v>3896.264236446613</v>
       </c>
       <c r="E39">
-        <v>1993.820935779248</v>
+        <v>2053.166635211323</v>
       </c>
       <c r="F39">
-        <v>2195.790878986792</v>
+        <v>2255.136578418867</v>
       </c>
       <c r="G39">
         <v>271</v>
@@ -4607,37 +4607,37 @@
         <v>187.31</v>
       </c>
       <c r="M39">
-        <v>440.9148085005477</v>
+        <v>452.8314249465085</v>
       </c>
       <c r="N39">
-        <v>-253.6048085005477</v>
+        <v>-265.5214249465085</v>
       </c>
       <c r="O39">
-        <v>-58.32910595512598</v>
+        <v>-61.06992773769696</v>
       </c>
       <c r="P39">
-        <v>-195.2757025454218</v>
+        <v>-204.4514972088115</v>
       </c>
       <c r="Q39">
-        <v>51.72429745457825</v>
+        <v>42.54850279118847</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2095391140803466</v>
+        <v>0.2121800675332554</v>
       </c>
       <c r="T39">
-        <v>2.53299201954451</v>
+        <v>2.573846729537164</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.09770889788553447</v>
+        <v>0.09513761109907302</v>
       </c>
       <c r="W39">
-        <v>0.1811800533045847</v>
+        <v>0.1816963676913061</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.4248212951544976</v>
+        <v>0.4136417873872741</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4653,22 +4653,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2005962615933147</v>
+        <v>0.2021462615933147</v>
       </c>
       <c r="C40">
-        <v>1912.127658027747</v>
+        <v>1814.154814556875</v>
       </c>
       <c r="D40">
-        <v>3896.264236446613</v>
+        <v>3857.637092407817</v>
       </c>
       <c r="E40">
-        <v>2053.166635211323</v>
+        <v>2112.512334643399</v>
       </c>
       <c r="F40">
-        <v>2255.136578418867</v>
+        <v>2314.482277850942</v>
       </c>
       <c r="G40">
         <v>271</v>
@@ -4689,37 +4689,37 @@
         <v>187.31</v>
       </c>
       <c r="M40">
-        <v>452.8314249465085</v>
+        <v>464.7480413924692</v>
       </c>
       <c r="N40">
-        <v>-265.5214249465085</v>
+        <v>-277.4380413924692</v>
       </c>
       <c r="O40">
-        <v>-61.06992773769696</v>
+        <v>-63.81074952026793</v>
       </c>
       <c r="P40">
-        <v>-204.4514972088115</v>
+        <v>-213.6272918722013</v>
       </c>
       <c r="Q40">
-        <v>42.54850279118847</v>
+        <v>33.37270812779869</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2121800675332554</v>
+        <v>0.2149076096239645</v>
       </c>
       <c r="T40">
-        <v>2.573846729537164</v>
+        <v>2.616040938218101</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.09513761109907302</v>
+        <v>0.09269818517345578</v>
       </c>
       <c r="W40">
-        <v>0.1816963676913061</v>
+        <v>0.1821862044171701</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4136417873872741</v>
+        <v>0.4030355877106773</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4735,22 +4735,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2021462615933147</v>
+        <v>0.2036962615933147</v>
       </c>
       <c r="C41">
-        <v>1814.154814556875</v>
+        <v>1716.940343357215</v>
       </c>
       <c r="D41">
-        <v>3857.637092407817</v>
+        <v>3819.768320640233</v>
       </c>
       <c r="E41">
-        <v>2112.512334643399</v>
+        <v>2171.858034075474</v>
       </c>
       <c r="F41">
-        <v>2314.482277850942</v>
+        <v>2373.827977283018</v>
       </c>
       <c r="G41">
         <v>271</v>
@@ -4771,37 +4771,37 @@
         <v>187.31</v>
       </c>
       <c r="M41">
-        <v>464.7480413924692</v>
+        <v>476.66465783843</v>
       </c>
       <c r="N41">
-        <v>-277.4380413924692</v>
+        <v>-289.35465783843</v>
       </c>
       <c r="O41">
-        <v>-63.81074952026793</v>
+        <v>-66.55157130283891</v>
       </c>
       <c r="P41">
-        <v>-213.6272918722013</v>
+        <v>-222.8030865355911</v>
       </c>
       <c r="Q41">
-        <v>33.37270812779869</v>
+        <v>24.19691346440891</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2149076096239645</v>
+        <v>0.2177260697843639</v>
       </c>
       <c r="T41">
-        <v>2.616040938218101</v>
+        <v>2.659641620521736</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.09269818517345578</v>
+        <v>0.09038073054411938</v>
       </c>
       <c r="W41">
-        <v>0.1821862044171701</v>
+        <v>0.1826515493067409</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.4030355877106773</v>
+        <v>0.3929596980179103</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4817,22 +4817,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2036962615933147</v>
+        <v>0.2052462615933147</v>
       </c>
       <c r="C42">
-        <v>1716.940343357215</v>
+        <v>1620.462127691591</v>
       </c>
       <c r="D42">
-        <v>3819.768320640233</v>
+        <v>3782.635804406685</v>
       </c>
       <c r="E42">
-        <v>2171.858034075474</v>
+        <v>2231.20373350755</v>
       </c>
       <c r="F42">
-        <v>2373.827977283018</v>
+        <v>2433.173676715093</v>
       </c>
       <c r="G42">
         <v>271</v>
@@ -4853,37 +4853,37 @@
         <v>187.31</v>
       </c>
       <c r="M42">
-        <v>476.66465783843</v>
+        <v>488.5812742843908</v>
       </c>
       <c r="N42">
-        <v>-289.35465783843</v>
+        <v>-301.2712742843908</v>
       </c>
       <c r="O42">
-        <v>-66.55157130283891</v>
+        <v>-69.29239308540987</v>
       </c>
       <c r="P42">
-        <v>-222.8030865355911</v>
+        <v>-231.9788811989809</v>
       </c>
       <c r="Q42">
-        <v>24.19691346440891</v>
+        <v>15.0211188010191</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2177260697843639</v>
+        <v>0.2206400709671497</v>
       </c>
       <c r="T42">
-        <v>2.659641620521736</v>
+        <v>2.704720292056002</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.09038073054411938</v>
+        <v>0.08817632248206768</v>
       </c>
       <c r="W42">
-        <v>0.1826515493067409</v>
+        <v>0.1830941944456008</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3929596980179103</v>
+        <v>0.3833753151394247</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4899,22 +4899,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2052462615933147</v>
+        <v>0.2067962615933147</v>
       </c>
       <c r="C43">
-        <v>1620.462127691591</v>
+        <v>1524.698902543044</v>
       </c>
       <c r="D43">
-        <v>3782.635804406685</v>
+        <v>3746.218278690213</v>
       </c>
       <c r="E43">
-        <v>2231.20373350755</v>
+        <v>2290.549432939625</v>
       </c>
       <c r="F43">
-        <v>2433.173676715093</v>
+        <v>2492.519376147169</v>
       </c>
       <c r="G43">
         <v>271</v>
@@ -4935,37 +4935,37 @@
         <v>187.31</v>
       </c>
       <c r="M43">
-        <v>488.5812742843908</v>
+        <v>500.4978907303515</v>
       </c>
       <c r="N43">
-        <v>-301.2712742843908</v>
+        <v>-313.1878907303515</v>
       </c>
       <c r="O43">
-        <v>-69.29239308540987</v>
+        <v>-72.03321486798085</v>
       </c>
       <c r="P43">
-        <v>-231.9788811989809</v>
+        <v>-241.1546758623707</v>
       </c>
       <c r="Q43">
-        <v>15.0211188010191</v>
+        <v>5.845324137629348</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2206400709671497</v>
+        <v>0.2236545549493419</v>
       </c>
       <c r="T43">
-        <v>2.704720292056002</v>
+        <v>2.751353400539727</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.08817632248206768</v>
+        <v>0.08607688623249465</v>
       </c>
       <c r="W43">
-        <v>0.1830941944456008</v>
+        <v>0.1835157612445151</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3833753151394247</v>
+        <v>0.3742473314456288</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4981,22 +4981,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2067962615933147</v>
+        <v>0.2083462615933147</v>
       </c>
       <c r="C44">
-        <v>1524.698902543044</v>
+        <v>1429.630214005886</v>
       </c>
       <c r="D44">
-        <v>3746.218278690213</v>
+        <v>3710.49528958513</v>
       </c>
       <c r="E44">
-        <v>2290.549432939625</v>
+        <v>2349.895132371701</v>
       </c>
       <c r="F44">
-        <v>2492.519376147169</v>
+        <v>2551.865075579244</v>
       </c>
       <c r="G44">
         <v>271</v>
@@ -5017,37 +5017,37 @@
         <v>187.31</v>
       </c>
       <c r="M44">
-        <v>500.4978907303515</v>
+        <v>512.4145071763122</v>
       </c>
       <c r="N44">
-        <v>-313.1878907303515</v>
+        <v>-325.1045071763122</v>
       </c>
       <c r="O44">
-        <v>-72.03321486798085</v>
+        <v>-74.77403665055181</v>
       </c>
       <c r="P44">
-        <v>-241.1546758623707</v>
+        <v>-250.3304705257604</v>
       </c>
       <c r="Q44">
-        <v>5.845324137629348</v>
+        <v>-3.330470525760404</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2236545549493419</v>
+        <v>0.2267748102993304</v>
       </c>
       <c r="T44">
-        <v>2.751353400539726</v>
+        <v>2.799622758443932</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.08607688623249465</v>
+        <v>0.08407509818057618</v>
       </c>
       <c r="W44">
-        <v>0.1835157612445151</v>
+        <v>0.1839177202853403</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3742473314456288</v>
+        <v>0.3655439051329399</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5063,22 +5063,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2083462615933147</v>
+        <v>0.2098962615933147</v>
       </c>
       <c r="C45">
-        <v>1429.630214005886</v>
+        <v>1335.236380978235</v>
       </c>
       <c r="D45">
-        <v>3710.49528958513</v>
+        <v>3675.447155989554</v>
       </c>
       <c r="E45">
-        <v>2349.895132371701</v>
+        <v>2409.240831803776</v>
       </c>
       <c r="F45">
-        <v>2551.865075579244</v>
+        <v>2611.21077501132</v>
       </c>
       <c r="G45">
         <v>271</v>
@@ -5099,37 +5099,37 @@
         <v>187.31</v>
       </c>
       <c r="M45">
-        <v>512.4145071763122</v>
+        <v>524.331123622273</v>
       </c>
       <c r="N45">
-        <v>-325.1045071763122</v>
+        <v>-337.021123622273</v>
       </c>
       <c r="O45">
-        <v>-74.77403665055181</v>
+        <v>-77.5148584331228</v>
       </c>
       <c r="P45">
-        <v>-250.3304705257604</v>
+        <v>-259.5062651891502</v>
       </c>
       <c r="Q45">
-        <v>-3.330470525760404</v>
+        <v>-12.50626518915021</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2267748102993304</v>
+        <v>0.2300065033403899</v>
       </c>
       <c r="T45">
-        <v>2.799622758443932</v>
+        <v>2.849616021987574</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.08407509818057618</v>
+        <v>0.08216430049465398</v>
       </c>
       <c r="W45">
-        <v>0.1839177202853403</v>
+        <v>0.1843014084606735</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3655439051329399</v>
+        <v>0.3572360891071912</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5145,22 +5145,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2098962615933147</v>
+        <v>0.2114462615933147</v>
       </c>
       <c r="C46">
-        <v>1335.236380978235</v>
+        <v>1241.498459005269</v>
       </c>
       <c r="D46">
-        <v>3675.447155989554</v>
+        <v>3641.054933448664</v>
       </c>
       <c r="E46">
-        <v>2409.240831803776</v>
+        <v>2468.586531235851</v>
       </c>
       <c r="F46">
-        <v>2611.21077501132</v>
+        <v>2670.556474443395</v>
       </c>
       <c r="G46">
         <v>271</v>
@@ -5181,37 +5181,37 @@
         <v>187.31</v>
       </c>
       <c r="M46">
-        <v>524.331123622273</v>
+        <v>536.2477400682337</v>
       </c>
       <c r="N46">
-        <v>-337.021123622273</v>
+        <v>-348.9377400682337</v>
       </c>
       <c r="O46">
-        <v>-77.5148584331228</v>
+        <v>-80.25568021569376</v>
       </c>
       <c r="P46">
-        <v>-259.5062651891502</v>
+        <v>-268.68205985254</v>
       </c>
       <c r="Q46">
-        <v>-12.50626518915021</v>
+        <v>-21.68205985253996</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2300065033403899</v>
+        <v>0.2333557124920333</v>
       </c>
       <c r="T46">
-        <v>2.849616021987574</v>
+        <v>2.901427222387348</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.08216430049465398</v>
+        <v>0.08033842715032834</v>
       </c>
       <c r="W46">
-        <v>0.1843014084606735</v>
+        <v>0.1846680438282141</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3572360891071912</v>
+        <v>0.3492975093492536</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2114462615933147</v>
+        <v>0.2129962615933147</v>
       </c>
       <c r="C47">
-        <v>1241.498459005269</v>
+        <v>1148.398206133638</v>
       </c>
       <c r="D47">
-        <v>3641.054933448664</v>
+        <v>3607.300380009108</v>
       </c>
       <c r="E47">
-        <v>2468.586531235851</v>
+        <v>2527.932230667927</v>
       </c>
       <c r="F47">
-        <v>2670.556474443395</v>
+        <v>2729.90217387547</v>
       </c>
       <c r="G47">
         <v>271</v>
@@ -5263,37 +5263,37 @@
         <v>187.31</v>
       </c>
       <c r="M47">
-        <v>536.2477400682337</v>
+        <v>548.1643565141945</v>
       </c>
       <c r="N47">
-        <v>-348.9377400682337</v>
+        <v>-360.8543565141945</v>
       </c>
       <c r="O47">
-        <v>-80.25568021569376</v>
+        <v>-82.99650199826475</v>
       </c>
       <c r="P47">
-        <v>-268.68205985254</v>
+        <v>-277.8578545159298</v>
       </c>
       <c r="Q47">
-        <v>-21.68205985253996</v>
+        <v>-30.85785451592977</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2333557124920333</v>
+        <v>0.236828966427071</v>
       </c>
       <c r="T47">
-        <v>2.901427222387348</v>
+        <v>2.955157356135262</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.08033842715032834</v>
+        <v>0.07859193960358206</v>
       </c>
       <c r="W47">
-        <v>0.1846680438282141</v>
+        <v>0.1850187385276007</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3492975093492536</v>
+        <v>0.3417040852329655</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5309,22 +5309,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2129962615933147</v>
+        <v>0.2145462615933147</v>
       </c>
       <c r="C48">
-        <v>1148.398206133638</v>
+        <v>1055.918050647719</v>
       </c>
       <c r="D48">
-        <v>3607.300380009108</v>
+        <v>3574.165923955265</v>
       </c>
       <c r="E48">
-        <v>2527.932230667927</v>
+        <v>2587.277930100002</v>
       </c>
       <c r="F48">
-        <v>2729.90217387547</v>
+        <v>2789.247873307546</v>
       </c>
       <c r="G48">
         <v>271</v>
@@ -5345,37 +5345,37 @@
         <v>187.31</v>
       </c>
       <c r="M48">
-        <v>548.1643565141945</v>
+        <v>560.0809729601552</v>
       </c>
       <c r="N48">
-        <v>-360.8543565141945</v>
+        <v>-372.7709729601552</v>
       </c>
       <c r="O48">
-        <v>-82.99650199826475</v>
+        <v>-85.73732378083571</v>
       </c>
       <c r="P48">
-        <v>-277.8578545159298</v>
+        <v>-287.0336491793195</v>
       </c>
       <c r="Q48">
-        <v>-30.85785451592977</v>
+        <v>-40.03364917931953</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.236828966427071</v>
+        <v>0.2404332865483365</v>
       </c>
       <c r="T48">
-        <v>2.955157356135262</v>
+        <v>3.010915042100078</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.07859193960358206</v>
+        <v>0.07691977067584628</v>
       </c>
       <c r="W48">
-        <v>0.1850187385276007</v>
+        <v>0.1853545100482901</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3417040852329655</v>
+        <v>0.3344337855471577</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5391,22 +5391,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2145462615933147</v>
+        <v>0.2160962615933147</v>
       </c>
       <c r="C49">
-        <v>1055.918050647719</v>
+        <v>964.0410605678157</v>
       </c>
       <c r="D49">
-        <v>3574.165923955265</v>
+        <v>3541.634633307437</v>
       </c>
       <c r="E49">
-        <v>2587.277930100002</v>
+        <v>2646.623629532078</v>
       </c>
       <c r="F49">
-        <v>2789.247873307546</v>
+        <v>2848.593572739621</v>
       </c>
       <c r="G49">
         <v>271</v>
@@ -5427,37 +5427,37 @@
         <v>187.31</v>
       </c>
       <c r="M49">
-        <v>560.0809729601552</v>
+        <v>571.9975894061159</v>
       </c>
       <c r="N49">
-        <v>-372.7709729601552</v>
+        <v>-384.6875894061159</v>
       </c>
       <c r="O49">
-        <v>-85.73732378083571</v>
+        <v>-88.47814556340667</v>
       </c>
       <c r="P49">
-        <v>-287.0336491793195</v>
+        <v>-296.2094438427093</v>
       </c>
       <c r="Q49">
-        <v>-40.03364917931953</v>
+        <v>-49.20944384270928</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2404332865483365</v>
+        <v>0.2441762343665737</v>
       </c>
       <c r="T49">
-        <v>3.010915042100078</v>
+        <v>3.068817254448156</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.07691977067584628</v>
+        <v>0.07531727545343282</v>
       </c>
       <c r="W49">
-        <v>0.1853545100482901</v>
+        <v>0.1856762910889507</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3344337855471577</v>
+        <v>0.3274664150149253</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5473,22 +5473,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2160962615933147</v>
+        <v>0.2176462615933146</v>
       </c>
       <c r="C50">
-        <v>964.0410605678162</v>
+        <v>872.7509147990627</v>
       </c>
       <c r="D50">
-        <v>3541.634633307438</v>
+        <v>3509.690186970759</v>
       </c>
       <c r="E50">
-        <v>2646.623629532078</v>
+        <v>2705.969328964153</v>
       </c>
       <c r="F50">
-        <v>2848.593572739621</v>
+        <v>2907.939272171697</v>
       </c>
       <c r="G50">
         <v>271</v>
@@ -5509,37 +5509,37 @@
         <v>187.31</v>
       </c>
       <c r="M50">
-        <v>571.9975894061159</v>
+        <v>583.9142058520767</v>
       </c>
       <c r="N50">
-        <v>-384.6875894061159</v>
+        <v>-396.6042058520767</v>
       </c>
       <c r="O50">
-        <v>-88.47814556340667</v>
+        <v>-91.21896734597766</v>
       </c>
       <c r="P50">
-        <v>-296.2094438427093</v>
+        <v>-305.3852385060991</v>
       </c>
       <c r="Q50">
-        <v>-49.20944384270928</v>
+        <v>-58.38523850609909</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2441762343665737</v>
+        <v>0.2480659644521928</v>
       </c>
       <c r="T50">
-        <v>3.068817254448156</v>
+        <v>3.128990141790277</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.07531727545343282</v>
+        <v>0.07378018819928113</v>
       </c>
       <c r="W50">
-        <v>0.1856762910889507</v>
+        <v>0.1859849382095844</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3274664150149253</v>
+        <v>0.3207834269533962</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5555,22 +5555,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2176462615933146</v>
+        <v>0.2191962615933147</v>
       </c>
       <c r="C51">
-        <v>872.7509147990627</v>
+        <v>782.0318758277313</v>
       </c>
       <c r="D51">
-        <v>3509.690186970759</v>
+        <v>3478.316847431503</v>
       </c>
       <c r="E51">
-        <v>2705.969328964153</v>
+        <v>2765.315028396229</v>
       </c>
       <c r="F51">
-        <v>2907.939272171697</v>
+        <v>2967.284971603772</v>
       </c>
       <c r="G51">
         <v>271</v>
@@ -5591,37 +5591,37 @@
         <v>187.31</v>
       </c>
       <c r="M51">
-        <v>583.9142058520767</v>
+        <v>595.8308222980374</v>
       </c>
       <c r="N51">
-        <v>-396.6042058520767</v>
+        <v>-408.5208222980374</v>
       </c>
       <c r="O51">
-        <v>-91.21896734597766</v>
+        <v>-93.95978912854862</v>
       </c>
       <c r="P51">
-        <v>-305.3852385060991</v>
+        <v>-314.5610331694888</v>
       </c>
       <c r="Q51">
-        <v>-58.38523850609909</v>
+        <v>-67.56103316948884</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2480659644521928</v>
+        <v>0.2521112837412366</v>
       </c>
       <c r="T51">
-        <v>3.128990141790277</v>
+        <v>3.191569944626083</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.07378018819928113</v>
+        <v>0.07230458443529551</v>
       </c>
       <c r="W51">
-        <v>0.1859849382095844</v>
+        <v>0.1862812394453927</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3207834269533962</v>
+        <v>0.3143677584143283</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5637,22 +5637,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2191962615933147</v>
+        <v>0.2207462615933146</v>
       </c>
       <c r="C52">
-        <v>782.0318758277313</v>
+        <v>691.8687638689917</v>
       </c>
       <c r="D52">
-        <v>3478.316847431503</v>
+        <v>3447.499434904839</v>
       </c>
       <c r="E52">
-        <v>2765.315028396229</v>
+        <v>2824.660727828304</v>
       </c>
       <c r="F52">
-        <v>2967.284971603772</v>
+        <v>3026.630671035848</v>
       </c>
       <c r="G52">
         <v>271</v>
@@ -5673,37 +5673,37 @@
         <v>187.31</v>
       </c>
       <c r="M52">
-        <v>595.8308222980374</v>
+        <v>607.7474387439983</v>
       </c>
       <c r="N52">
-        <v>-408.5208222980374</v>
+        <v>-420.4374387439983</v>
       </c>
       <c r="O52">
-        <v>-93.95978912854862</v>
+        <v>-96.7006109111196</v>
       </c>
       <c r="P52">
-        <v>-314.5610331694888</v>
+        <v>-323.7368278328786</v>
       </c>
       <c r="Q52">
-        <v>-67.56103316948884</v>
+        <v>-76.73682783287865</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2521112837412366</v>
+        <v>0.2563217181033027</v>
       </c>
       <c r="T52">
-        <v>3.191569944626083</v>
+        <v>3.256704025128656</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.07230458443529551</v>
+        <v>0.07088684748558383</v>
       </c>
       <c r="W52">
-        <v>0.1862812394453927</v>
+        <v>0.1865659210248948</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3143677584143283</v>
+        <v>0.3082036847199296</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5719,22 +5719,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2207462615933146</v>
+        <v>0.2222962615933147</v>
       </c>
       <c r="C53">
-        <v>691.8687638689917</v>
+        <v>602.246932376876</v>
       </c>
       <c r="D53">
-        <v>3447.499434904839</v>
+        <v>3417.223302844799</v>
       </c>
       <c r="E53">
-        <v>2824.660727828304</v>
+        <v>2884.006427260379</v>
       </c>
       <c r="F53">
-        <v>3026.630671035848</v>
+        <v>3085.976370467923</v>
       </c>
       <c r="G53">
         <v>271</v>
@@ -5755,37 +5755,37 @@
         <v>187.31</v>
       </c>
       <c r="M53">
-        <v>607.7474387439983</v>
+        <v>619.664055189959</v>
       </c>
       <c r="N53">
-        <v>-420.4374387439983</v>
+        <v>-432.354055189959</v>
       </c>
       <c r="O53">
-        <v>-96.7006109111196</v>
+        <v>-99.44143269369056</v>
       </c>
       <c r="P53">
-        <v>-323.7368278328786</v>
+        <v>-332.9126224962684</v>
       </c>
       <c r="Q53">
-        <v>-76.73682783287865</v>
+        <v>-85.9126224962684</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2563217181033027</v>
+        <v>0.2607075872304548</v>
       </c>
       <c r="T53">
-        <v>3.256704025128656</v>
+        <v>3.324552025652169</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.07088684748558383</v>
+        <v>0.06952363888009183</v>
       </c>
       <c r="W53">
-        <v>0.1865659210248948</v>
+        <v>0.1868396533128776</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3082036847199296</v>
+        <v>0.302276690783008</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5801,22 +5801,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2222962615933147</v>
+        <v>0.2238462615933147</v>
       </c>
       <c r="C54">
-        <v>602.246932376876</v>
+        <v>513.1522448334526</v>
       </c>
       <c r="D54">
-        <v>3417.223302844799</v>
+        <v>3387.474314733451</v>
       </c>
       <c r="E54">
-        <v>2884.006427260379</v>
+        <v>2943.352126692455</v>
       </c>
       <c r="F54">
-        <v>3085.976370467923</v>
+        <v>3145.322069899998</v>
       </c>
       <c r="G54">
         <v>271</v>
@@ -5837,37 +5837,37 @@
         <v>187.31</v>
       </c>
       <c r="M54">
-        <v>619.664055189959</v>
+        <v>631.5806716359198</v>
       </c>
       <c r="N54">
-        <v>-432.354055189959</v>
+        <v>-444.2706716359198</v>
       </c>
       <c r="O54">
-        <v>-99.44143269369056</v>
+        <v>-102.1822544762615</v>
       </c>
       <c r="P54">
-        <v>-332.9126224962684</v>
+        <v>-342.0884171596582</v>
       </c>
       <c r="Q54">
-        <v>-85.9126224962684</v>
+        <v>-95.08841715965821</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2607075872304548</v>
+        <v>0.265280089086422</v>
       </c>
       <c r="T54">
-        <v>3.324552025652169</v>
+        <v>3.395287175134131</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.06952363888009183</v>
+        <v>0.06821187210876933</v>
       </c>
       <c r="W54">
-        <v>0.1868396533128776</v>
+        <v>0.1871030560805591</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.302276690783008</v>
+        <v>0.2965733569946493</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5883,22 +5883,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2238462615933147</v>
+        <v>0.2253962615933147</v>
       </c>
       <c r="C55">
-        <v>513.1522448334526</v>
+        <v>424.5710527399178</v>
       </c>
       <c r="D55">
-        <v>3387.474314733451</v>
+        <v>3358.238822071992</v>
       </c>
       <c r="E55">
-        <v>2943.352126692455</v>
+        <v>3002.697826124531</v>
       </c>
       <c r="F55">
-        <v>3145.322069899998</v>
+        <v>3204.667769332074</v>
       </c>
       <c r="G55">
         <v>271</v>
@@ -5919,37 +5919,37 @@
         <v>187.31</v>
       </c>
       <c r="M55">
-        <v>631.5806716359198</v>
+        <v>643.4972880818806</v>
       </c>
       <c r="N55">
-        <v>-444.2706716359198</v>
+        <v>-456.1872880818806</v>
       </c>
       <c r="O55">
-        <v>-102.1822544762615</v>
+        <v>-104.9230762588325</v>
       </c>
       <c r="P55">
-        <v>-342.0884171596582</v>
+        <v>-351.2642118230481</v>
       </c>
       <c r="Q55">
-        <v>-95.08841715965821</v>
+        <v>-104.2642118230481</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.265280089086422</v>
+        <v>0.2700513953709094</v>
       </c>
       <c r="T55">
-        <v>3.395287175134131</v>
+        <v>3.469097765897916</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.06821187210876933</v>
+        <v>0.06694868929194027</v>
       </c>
       <c r="W55">
-        <v>0.1871030560805591</v>
+        <v>0.1873567031901784</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2965733569946493</v>
+        <v>0.2910812577910447</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5965,22 +5965,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2253962615933147</v>
+        <v>0.2269462615933147</v>
       </c>
       <c r="C56">
-        <v>424.5710527399178</v>
+        <v>336.490174737623</v>
       </c>
       <c r="D56">
-        <v>3358.238822071992</v>
+        <v>3329.503643501773</v>
       </c>
       <c r="E56">
-        <v>3002.697826124531</v>
+        <v>3062.043525556606</v>
       </c>
       <c r="F56">
-        <v>3204.667769332074</v>
+        <v>3264.01346876415</v>
       </c>
       <c r="G56">
         <v>271</v>
@@ -6001,37 +6001,37 @@
         <v>187.31</v>
       </c>
       <c r="M56">
-        <v>643.4972880818806</v>
+        <v>655.4139045278413</v>
       </c>
       <c r="N56">
-        <v>-456.1872880818806</v>
+        <v>-468.1039045278413</v>
       </c>
       <c r="O56">
-        <v>-104.9230762588325</v>
+        <v>-107.6638980414035</v>
       </c>
       <c r="P56">
-        <v>-351.2642118230481</v>
+        <v>-360.4400064864378</v>
       </c>
       <c r="Q56">
-        <v>-104.2642118230481</v>
+        <v>-113.4400064864378</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2700513953709094</v>
+        <v>0.2750347597124852</v>
       </c>
       <c r="T56">
-        <v>3.469097765897916</v>
+        <v>3.546188827362315</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.06694868929194027</v>
+        <v>0.06573144039572318</v>
       </c>
       <c r="W56">
-        <v>0.1873567031901784</v>
+        <v>0.1876011267685388</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2910812577910447</v>
+        <v>0.2857888712857529</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6047,22 +6047,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2269462615933147</v>
+        <v>0.2284962615933147</v>
       </c>
       <c r="C57">
-        <v>336.490174737623</v>
+        <v>248.8968767919255</v>
       </c>
       <c r="D57">
-        <v>3329.503643501773</v>
+        <v>3301.256044988151</v>
       </c>
       <c r="E57">
-        <v>3062.043525556606</v>
+        <v>3121.389224988682</v>
       </c>
       <c r="F57">
-        <v>3264.01346876415</v>
+        <v>3323.359168196225</v>
       </c>
       <c r="G57">
         <v>271</v>
@@ -6083,37 +6083,37 @@
         <v>187.31</v>
       </c>
       <c r="M57">
-        <v>655.4139045278413</v>
+        <v>667.3305209738021</v>
       </c>
       <c r="N57">
-        <v>-468.1039045278413</v>
+        <v>-480.0205209738021</v>
       </c>
       <c r="O57">
-        <v>-107.6638980414035</v>
+        <v>-110.4047198239745</v>
       </c>
       <c r="P57">
-        <v>-360.4400064864378</v>
+        <v>-369.6158011498276</v>
       </c>
       <c r="Q57">
-        <v>-113.4400064864378</v>
+        <v>-122.6158011498276</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2750347597124852</v>
+        <v>0.2802446406150416</v>
       </c>
       <c r="T57">
-        <v>3.546188827362315</v>
+        <v>3.626784027984185</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.06573144039572318</v>
+        <v>0.06455766467437096</v>
       </c>
       <c r="W57">
-        <v>0.1876011267685388</v>
+        <v>0.1878368209333863</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2857888712857529</v>
+        <v>0.2806854985842216</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6129,22 +6129,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2284962615933147</v>
+        <v>0.2300462615933146</v>
       </c>
       <c r="C58">
-        <v>248.8968767919255</v>
+        <v>161.7788533762769</v>
       </c>
       <c r="D58">
-        <v>3301.256044988151</v>
+        <v>3273.483721004578</v>
       </c>
       <c r="E58">
-        <v>3121.389224988682</v>
+        <v>3180.734924420757</v>
       </c>
       <c r="F58">
-        <v>3323.359168196225</v>
+        <v>3382.704867628301</v>
       </c>
       <c r="G58">
         <v>271</v>
@@ -6165,37 +6165,37 @@
         <v>187.31</v>
       </c>
       <c r="M58">
-        <v>667.3305209738021</v>
+        <v>679.2471374197628</v>
       </c>
       <c r="N58">
-        <v>-480.0205209738021</v>
+        <v>-491.9371374197628</v>
       </c>
       <c r="O58">
-        <v>-110.4047198239745</v>
+        <v>-113.1455416065455</v>
       </c>
       <c r="P58">
-        <v>-369.6158011498276</v>
+        <v>-378.7915958132173</v>
       </c>
       <c r="Q58">
-        <v>-122.6158011498276</v>
+        <v>-131.7915958132173</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2802446406150416</v>
+        <v>0.2856968415595775</v>
       </c>
       <c r="T58">
-        <v>3.626784027984185</v>
+        <v>3.711127842588469</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.06455766467437096</v>
+        <v>0.06342507406604869</v>
       </c>
       <c r="W58">
-        <v>0.1878368209333863</v>
+        <v>0.1880642451275374</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2806854985842216</v>
+        <v>0.275761191591516</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6211,22 +6211,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2300462615933146</v>
+        <v>0.2315962615933146</v>
       </c>
       <c r="C59">
-        <v>161.7788533762769</v>
+        <v>75.12420959814517</v>
       </c>
       <c r="D59">
-        <v>3273.483721004578</v>
+        <v>3246.174776658521</v>
       </c>
       <c r="E59">
-        <v>3180.734924420757</v>
+        <v>3240.080623852833</v>
       </c>
       <c r="F59">
-        <v>3382.704867628301</v>
+        <v>3442.050567060376</v>
       </c>
       <c r="G59">
         <v>271</v>
@@ -6247,37 +6247,37 @@
         <v>187.31</v>
       </c>
       <c r="M59">
-        <v>679.2471374197628</v>
+        <v>691.1637538657235</v>
       </c>
       <c r="N59">
-        <v>-491.9371374197628</v>
+        <v>-503.8537538657235</v>
       </c>
       <c r="O59">
-        <v>-113.1455416065455</v>
+        <v>-115.8863633891164</v>
       </c>
       <c r="P59">
-        <v>-378.7915958132173</v>
+        <v>-387.9673904766071</v>
       </c>
       <c r="Q59">
-        <v>-131.7915958132173</v>
+        <v>-140.9673904766071</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2856968415595775</v>
+        <v>0.2914086711205198</v>
       </c>
       <c r="T59">
-        <v>3.711127842588469</v>
+        <v>3.799488029316766</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.06342507406604869</v>
+        <v>0.06233153830628922</v>
       </c>
       <c r="W59">
-        <v>0.1880642451275374</v>
+        <v>0.1882838271080971</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.275761191591516</v>
+        <v>0.2710066882882141</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2315962615933146</v>
+        <v>0.2331462615933146</v>
       </c>
       <c r="C60">
-        <v>75.12420959814563</v>
+        <v>-11.07855578778936</v>
       </c>
       <c r="D60">
-        <v>3246.174776658521</v>
+        <v>3219.317710704662</v>
       </c>
       <c r="E60">
-        <v>3240.080623852832</v>
+        <v>3299.426323284908</v>
       </c>
       <c r="F60">
-        <v>3442.050567060376</v>
+        <v>3501.396266492451</v>
       </c>
       <c r="G60">
         <v>271</v>
@@ -6329,37 +6329,37 @@
         <v>187.31</v>
       </c>
       <c r="M60">
-        <v>691.1637538657235</v>
+        <v>703.0803703116842</v>
       </c>
       <c r="N60">
-        <v>-503.8537538657235</v>
+        <v>-515.7703703116842</v>
       </c>
       <c r="O60">
-        <v>-115.8863633891164</v>
+        <v>-118.6271851716874</v>
       </c>
       <c r="P60">
-        <v>-387.9673904766071</v>
+        <v>-397.1431851399968</v>
       </c>
       <c r="Q60">
-        <v>-140.9673904766071</v>
+        <v>-150.1431851399968</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2914086711205198</v>
+        <v>0.2973991265137032</v>
       </c>
       <c r="T60">
-        <v>3.799488029316765</v>
+        <v>3.892158469056198</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.06233153830628922</v>
+        <v>0.06127507155533518</v>
       </c>
       <c r="W60">
-        <v>0.1882838271080971</v>
+        <v>0.1884959656316887</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2710066882882141</v>
+        <v>0.2664133545884138</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6375,22 +6375,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2331462615933146</v>
+        <v>0.2346962615933146</v>
       </c>
       <c r="C61">
-        <v>-11.07855578778936</v>
+        <v>-96.84056653011839</v>
       </c>
       <c r="D61">
-        <v>3219.317710704662</v>
+        <v>3192.901399394408</v>
       </c>
       <c r="E61">
-        <v>3299.426323284908</v>
+        <v>3358.772022716983</v>
       </c>
       <c r="F61">
-        <v>3501.396266492451</v>
+        <v>3560.741965924527</v>
       </c>
       <c r="G61">
         <v>271</v>
@@ -6411,37 +6411,37 @@
         <v>187.31</v>
       </c>
       <c r="M61">
-        <v>703.0803703116842</v>
+        <v>714.996986757645</v>
       </c>
       <c r="N61">
-        <v>-515.7703703116842</v>
+        <v>-527.6869867576449</v>
       </c>
       <c r="O61">
-        <v>-118.6271851716874</v>
+        <v>-121.3680069542583</v>
       </c>
       <c r="P61">
-        <v>-397.1431851399968</v>
+        <v>-406.3189798033866</v>
       </c>
       <c r="Q61">
-        <v>-150.1431851399968</v>
+        <v>-159.3189798033866</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2973991265137032</v>
+        <v>0.3036891046765458</v>
       </c>
       <c r="T61">
-        <v>3.892158469056198</v>
+        <v>3.989462430782603</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.06127507155533518</v>
+        <v>0.06025382036274626</v>
       </c>
       <c r="W61">
-        <v>0.1884959656316887</v>
+        <v>0.1887010328711606</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2664133545884138</v>
+        <v>0.2619731320119403</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6457,22 +6457,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2346962615933146</v>
+        <v>0.2362462615933147</v>
       </c>
       <c r="C62">
-        <v>-96.84056653011839</v>
+        <v>-182.1725842425171</v>
       </c>
       <c r="D62">
-        <v>3192.901399394408</v>
+        <v>3166.915081114085</v>
       </c>
       <c r="E62">
-        <v>3358.772022716983</v>
+        <v>3418.117722149058</v>
       </c>
       <c r="F62">
-        <v>3560.741965924527</v>
+        <v>3620.087665356602</v>
       </c>
       <c r="G62">
         <v>271</v>
@@ -6493,37 +6493,37 @@
         <v>187.31</v>
       </c>
       <c r="M62">
-        <v>714.996986757645</v>
+        <v>726.9136032036057</v>
       </c>
       <c r="N62">
-        <v>-527.6869867576449</v>
+        <v>-539.6036032036056</v>
       </c>
       <c r="O62">
-        <v>-121.3680069542583</v>
+        <v>-124.1088287368293</v>
       </c>
       <c r="P62">
-        <v>-406.3189798033866</v>
+        <v>-415.4947744667763</v>
       </c>
       <c r="Q62">
-        <v>-159.3189798033866</v>
+        <v>-168.4947744667763</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3036891046765458</v>
+        <v>0.3103016458220983</v>
       </c>
       <c r="T62">
-        <v>3.989462430782603</v>
+        <v>4.091756339264209</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.06025382036274626</v>
+        <v>0.05926605281581598</v>
       </c>
       <c r="W62">
-        <v>0.1887010328711606</v>
+        <v>0.1888993765945842</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2619731320119403</v>
+        <v>0.2576784905035479</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6539,22 +6539,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2362462615933147</v>
+        <v>0.2377962615933146</v>
       </c>
       <c r="C63">
-        <v>-182.1725842425171</v>
+        <v>-267.0850230214469</v>
       </c>
       <c r="D63">
-        <v>3166.915081114085</v>
+        <v>3141.348341767231</v>
       </c>
       <c r="E63">
-        <v>3418.117722149058</v>
+        <v>3477.463421581134</v>
       </c>
       <c r="F63">
-        <v>3620.087665356602</v>
+        <v>3679.433364788677</v>
       </c>
       <c r="G63">
         <v>271</v>
@@ -6575,37 +6575,37 @@
         <v>187.31</v>
       </c>
       <c r="M63">
-        <v>726.9136032036057</v>
+        <v>738.8302196495664</v>
       </c>
       <c r="N63">
-        <v>-539.6036032036056</v>
+        <v>-551.5202196495663</v>
       </c>
       <c r="O63">
-        <v>-124.1088287368293</v>
+        <v>-126.8496505194003</v>
       </c>
       <c r="P63">
-        <v>-415.4947744667763</v>
+        <v>-424.6705691301661</v>
       </c>
       <c r="Q63">
-        <v>-168.4947744667763</v>
+        <v>-177.6705691301661</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3103016458220983</v>
+        <v>0.3172622154489956</v>
       </c>
       <c r="T63">
-        <v>4.091756339264209</v>
+        <v>4.199434137665898</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.05926605281581598</v>
+        <v>0.05831014873814154</v>
       </c>
       <c r="W63">
-        <v>0.1888993765945842</v>
+        <v>0.1890913221333812</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2576784905035479</v>
+        <v>0.2535223858180068</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6621,22 +6621,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2377962615933146</v>
+        <v>0.2393462615933146</v>
       </c>
       <c r="C64">
-        <v>-267.0850230214469</v>
+        <v>-351.5879633614877</v>
       </c>
       <c r="D64">
-        <v>3141.348341767231</v>
+        <v>3116.191100859265</v>
       </c>
       <c r="E64">
-        <v>3477.463421581134</v>
+        <v>3536.809121013209</v>
       </c>
       <c r="F64">
-        <v>3679.433364788677</v>
+        <v>3738.779064220753</v>
       </c>
       <c r="G64">
         <v>271</v>
@@ -6657,37 +6657,37 @@
         <v>187.31</v>
       </c>
       <c r="M64">
-        <v>738.8302196495664</v>
+        <v>750.7468360955272</v>
       </c>
       <c r="N64">
-        <v>-551.5202196495663</v>
+        <v>-563.4368360955273</v>
       </c>
       <c r="O64">
-        <v>-126.8496505194003</v>
+        <v>-129.5904723019713</v>
       </c>
       <c r="P64">
-        <v>-424.6705691301661</v>
+        <v>-433.846363793556</v>
       </c>
       <c r="Q64">
-        <v>-177.6705691301661</v>
+        <v>-186.846363793556</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3172622154489956</v>
+        <v>0.3245990320827522</v>
       </c>
       <c r="T64">
-        <v>4.199434137665898</v>
+        <v>4.312932357602814</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.05831014873814154</v>
+        <v>0.0573845908216631</v>
       </c>
       <c r="W64">
-        <v>0.1890913221333812</v>
+        <v>0.18927717416301</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2535223858180068</v>
+        <v>0.2494982209637525</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6703,22 +6703,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2393462615933146</v>
+        <v>0.2408962615933146</v>
       </c>
       <c r="C65">
-        <v>-351.5879633614877</v>
+        <v>-435.6911654073265</v>
       </c>
       <c r="D65">
-        <v>3116.191100859265</v>
+        <v>3091.433598245502</v>
       </c>
       <c r="E65">
-        <v>3536.809121013209</v>
+        <v>3596.154820445285</v>
       </c>
       <c r="F65">
-        <v>3738.779064220753</v>
+        <v>3798.124763652828</v>
       </c>
       <c r="G65">
         <v>271</v>
@@ -6739,37 +6739,37 @@
         <v>187.31</v>
       </c>
       <c r="M65">
-        <v>750.7468360955272</v>
+        <v>762.6634525414879</v>
       </c>
       <c r="N65">
-        <v>-563.4368360955273</v>
+        <v>-575.353452541488</v>
       </c>
       <c r="O65">
-        <v>-129.5904723019713</v>
+        <v>-132.3312940845422</v>
       </c>
       <c r="P65">
-        <v>-433.846363793556</v>
+        <v>-443.0221584569457</v>
       </c>
       <c r="Q65">
-        <v>-186.846363793556</v>
+        <v>-196.0221584569457</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3245990320827522</v>
+        <v>0.3323434496406064</v>
       </c>
       <c r="T65">
-        <v>4.312932357602814</v>
+        <v>4.432736034202892</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.0573845908216631</v>
+        <v>0.05648795659007462</v>
       </c>
       <c r="W65">
-        <v>0.18927717416301</v>
+        <v>0.189457218316713</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2494982209637525</v>
+        <v>0.2455998112611939</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6785,22 +6785,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2408962615933146</v>
+        <v>0.2424462615933147</v>
       </c>
       <c r="C66">
-        <v>-435.6911654073265</v>
+        <v>-519.404081579024</v>
       </c>
       <c r="D66">
-        <v>3091.433598245502</v>
+        <v>3067.06638150588</v>
       </c>
       <c r="E66">
-        <v>3596.154820445285</v>
+        <v>3655.500519877361</v>
       </c>
       <c r="F66">
-        <v>3798.124763652828</v>
+        <v>3857.470463084904</v>
       </c>
       <c r="G66">
         <v>271</v>
@@ -6821,37 +6821,37 @@
         <v>187.31</v>
       </c>
       <c r="M66">
-        <v>762.6634525414879</v>
+        <v>774.5800689874487</v>
       </c>
       <c r="N66">
-        <v>-575.353452541488</v>
+        <v>-587.2700689874487</v>
       </c>
       <c r="O66">
-        <v>-132.3312940845422</v>
+        <v>-135.0721158671132</v>
       </c>
       <c r="P66">
-        <v>-443.0221584569457</v>
+        <v>-452.1979531203355</v>
       </c>
       <c r="Q66">
-        <v>-196.0221584569457</v>
+        <v>-205.1979531203355</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3323434496406064</v>
+        <v>0.3405304053446239</v>
       </c>
       <c r="T66">
-        <v>4.432736034202892</v>
+        <v>4.559385635180119</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.05648795659007462</v>
+        <v>0.05561891110407347</v>
       </c>
       <c r="W66">
-        <v>0.189457218316713</v>
+        <v>0.1896317226503021</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2455998112611939</v>
+        <v>0.2418213526264065</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6867,22 +6867,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2424462615933147</v>
+        <v>0.2439962615933147</v>
       </c>
       <c r="C67">
-        <v>-519.404081579024</v>
+        <v>-602.7358686048647</v>
       </c>
       <c r="D67">
-        <v>3067.06638150588</v>
+        <v>3043.080293912115</v>
       </c>
       <c r="E67">
-        <v>3655.500519877361</v>
+        <v>3714.846219309436</v>
       </c>
       <c r="F67">
-        <v>3857.470463084904</v>
+        <v>3916.81616251698</v>
       </c>
       <c r="G67">
         <v>271</v>
@@ -6903,37 +6903,37 @@
         <v>187.31</v>
       </c>
       <c r="M67">
-        <v>774.5800689874487</v>
+        <v>786.4966854334095</v>
       </c>
       <c r="N67">
-        <v>-587.2700689874487</v>
+        <v>-599.1866854334096</v>
       </c>
       <c r="O67">
-        <v>-135.0721158671132</v>
+        <v>-137.8129376496842</v>
       </c>
       <c r="P67">
-        <v>-452.1979531203355</v>
+        <v>-461.3737477837254</v>
       </c>
       <c r="Q67">
-        <v>-205.1979531203355</v>
+        <v>-214.3737477837254</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3405304053446239</v>
+        <v>0.3491989466782893</v>
       </c>
       <c r="T67">
-        <v>4.559385635180119</v>
+        <v>4.693485212685417</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.05561891110407347</v>
+        <v>0.05477620032976931</v>
       </c>
       <c r="W67">
-        <v>0.1896317226503021</v>
+        <v>0.1898009389737823</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2418213526264065</v>
+        <v>0.2381573927381274</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6949,22 +6949,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2439962615933147</v>
+        <v>0.2455462615933147</v>
       </c>
       <c r="C68">
-        <v>-602.7358686048647</v>
+        <v>-685.6953989939734</v>
       </c>
       <c r="D68">
-        <v>3043.080293912115</v>
+        <v>3019.466462955082</v>
       </c>
       <c r="E68">
-        <v>3714.846219309436</v>
+        <v>3774.191918741511</v>
       </c>
       <c r="F68">
-        <v>3916.81616251698</v>
+        <v>3976.161861949055</v>
       </c>
       <c r="G68">
         <v>271</v>
@@ -6985,37 +6985,37 @@
         <v>187.31</v>
       </c>
       <c r="M68">
-        <v>786.4966854334095</v>
+        <v>798.4133018793702</v>
       </c>
       <c r="N68">
-        <v>-599.1866854334096</v>
+        <v>-611.1033018793703</v>
       </c>
       <c r="O68">
-        <v>-137.8129376496842</v>
+        <v>-140.5537594322552</v>
       </c>
       <c r="P68">
-        <v>-461.3737477837254</v>
+        <v>-470.5495424471151</v>
       </c>
       <c r="Q68">
-        <v>-214.3737477837254</v>
+        <v>-223.5495424471151</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3491989466782893</v>
+        <v>0.358392854153389</v>
       </c>
       <c r="T68">
-        <v>4.693485212685417</v>
+        <v>4.835712037312248</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.05477620032976931</v>
+        <v>0.0539586451009668</v>
       </c>
       <c r="W68">
-        <v>0.1898009389737823</v>
+        <v>0.1899651040637259</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2381573927381274</v>
+        <v>0.2346028047868121</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7031,22 +7031,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2455462615933147</v>
+        <v>0.2470962615933147</v>
       </c>
       <c r="C69">
-        <v>-685.6953989939734</v>
+        <v>-768.2912719788778</v>
       </c>
       <c r="D69">
-        <v>3019.466462955082</v>
+        <v>2996.216289402253</v>
       </c>
       <c r="E69">
-        <v>3774.191918741511</v>
+        <v>3833.537618173587</v>
       </c>
       <c r="F69">
-        <v>3976.161861949055</v>
+        <v>4035.50756138113</v>
       </c>
       <c r="G69">
         <v>271</v>
@@ -7067,37 +7067,37 @@
         <v>187.31</v>
       </c>
       <c r="M69">
-        <v>798.4133018793702</v>
+        <v>810.3299183253311</v>
       </c>
       <c r="N69">
-        <v>-611.1033018793703</v>
+        <v>-623.019918325331</v>
       </c>
       <c r="O69">
-        <v>-140.5537594322552</v>
+        <v>-143.2945812148261</v>
       </c>
       <c r="P69">
-        <v>-470.5495424471151</v>
+        <v>-479.7253371105048</v>
       </c>
       <c r="Q69">
-        <v>-223.5495424471151</v>
+        <v>-232.7253371105048</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.358392854153389</v>
+        <v>0.3681613808456823</v>
       </c>
       <c r="T69">
-        <v>4.835712037312248</v>
+        <v>4.986828038478255</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.0539586451009668</v>
+        <v>0.05316513561418787</v>
       </c>
       <c r="W69">
-        <v>0.1899651040637259</v>
+        <v>0.1901244407686711</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2346028047868121</v>
+        <v>0.2311527635399473</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7113,22 +7113,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2470962615933147</v>
+        <v>0.2486462615933147</v>
       </c>
       <c r="C70">
-        <v>-768.2912719788778</v>
+        <v>-850.5318239563981</v>
       </c>
       <c r="D70">
-        <v>2996.216289402253</v>
+        <v>2973.321436856808</v>
       </c>
       <c r="E70">
-        <v>3833.537618173587</v>
+        <v>3892.883317605662</v>
       </c>
       <c r="F70">
-        <v>4035.50756138113</v>
+        <v>4094.853260813206</v>
       </c>
       <c r="G70">
         <v>271</v>
@@ -7149,37 +7149,37 @@
         <v>187.31</v>
       </c>
       <c r="M70">
-        <v>810.3299183253311</v>
+        <v>822.2465347712917</v>
       </c>
       <c r="N70">
-        <v>-623.019918325331</v>
+        <v>-634.9365347712917</v>
       </c>
       <c r="O70">
-        <v>-143.2945812148261</v>
+        <v>-146.0354029973971</v>
       </c>
       <c r="P70">
-        <v>-479.7253371105048</v>
+        <v>-488.9011317738946</v>
       </c>
       <c r="Q70">
-        <v>-232.7253371105048</v>
+        <v>-241.9011317738946</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3681613808456823</v>
+        <v>0.3785601350665108</v>
       </c>
       <c r="T70">
-        <v>4.986828038478255</v>
+        <v>5.147693459074328</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.05316513561418787</v>
+        <v>0.05239462640238805</v>
       </c>
       <c r="W70">
-        <v>0.1901244407686711</v>
+        <v>0.1902791590184005</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2311527635399473</v>
+        <v>0.2278027234886437</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7195,22 +7195,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2486462615933147</v>
+        <v>0.2501962615933147</v>
       </c>
       <c r="C71">
-        <v>-850.5318239563981</v>
+        <v>-932.4251384534573</v>
       </c>
       <c r="D71">
-        <v>2973.321436856808</v>
+        <v>2950.773821791824</v>
       </c>
       <c r="E71">
-        <v>3892.883317605662</v>
+        <v>3952.229017037738</v>
       </c>
       <c r="F71">
-        <v>4094.853260813206</v>
+        <v>4154.198960245281</v>
       </c>
       <c r="G71">
         <v>271</v>
@@ -7231,37 +7231,37 @@
         <v>187.31</v>
       </c>
       <c r="M71">
-        <v>822.2465347712917</v>
+        <v>834.1631512172526</v>
       </c>
       <c r="N71">
-        <v>-634.9365347712917</v>
+        <v>-646.8531512172526</v>
       </c>
       <c r="O71">
-        <v>-146.0354029973971</v>
+        <v>-148.7762247799681</v>
       </c>
       <c r="P71">
-        <v>-488.9011317738946</v>
+        <v>-498.0769264372845</v>
       </c>
       <c r="Q71">
-        <v>-241.9011317738946</v>
+        <v>-251.0769264372845</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3785601350665108</v>
+        <v>0.3896521395687278</v>
       </c>
       <c r="T71">
-        <v>5.147693459074328</v>
+        <v>5.319283241043472</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.05239462640238805</v>
+        <v>0.05164613173949679</v>
       </c>
       <c r="W71">
-        <v>0.1902791590184005</v>
+        <v>0.1904294567467091</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2278027234886437</v>
+        <v>0.2245483988673772</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7277,22 +7277,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2501962615933147</v>
+        <v>0.2517462615933147</v>
       </c>
       <c r="C72">
-        <v>-932.4251384534573</v>
+        <v>-1013.979055642889</v>
       </c>
       <c r="D72">
-        <v>2950.773821791824</v>
+        <v>2928.565604034468</v>
       </c>
       <c r="E72">
-        <v>3952.229017037738</v>
+        <v>4011.574716469814</v>
       </c>
       <c r="F72">
-        <v>4154.198960245281</v>
+        <v>4213.544659677357</v>
       </c>
       <c r="G72">
         <v>271</v>
@@ -7313,37 +7313,37 @@
         <v>187.31</v>
       </c>
       <c r="M72">
-        <v>834.1631512172526</v>
+        <v>846.0797676632134</v>
       </c>
       <c r="N72">
-        <v>-646.8531512172526</v>
+        <v>-658.7697676632133</v>
       </c>
       <c r="O72">
-        <v>-148.7762247799681</v>
+        <v>-151.5170465625391</v>
       </c>
       <c r="P72">
-        <v>-498.0769264372845</v>
+        <v>-507.2527211006743</v>
       </c>
       <c r="Q72">
-        <v>-251.0769264372845</v>
+        <v>-260.2527211006743</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3896521395687278</v>
+        <v>0.401509109898684</v>
       </c>
       <c r="T72">
-        <v>5.319283241043472</v>
+        <v>5.502706801079455</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.05164613173949679</v>
+        <v>0.05091872143330668</v>
       </c>
       <c r="W72">
-        <v>0.1904294567467091</v>
+        <v>0.190575520736192</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2245483988673772</v>
+        <v>0.221385745362203</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7359,22 +7359,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2517462615933146</v>
+        <v>0.2532962615933146</v>
       </c>
       <c r="C73">
-        <v>-1013.979055642887</v>
+        <v>-1095.201181432707</v>
       </c>
       <c r="D73">
-        <v>2928.56560403447</v>
+        <v>2906.689177676726</v>
       </c>
       <c r="E73">
-        <v>4011.574716469813</v>
+        <v>4070.920415901889</v>
       </c>
       <c r="F73">
-        <v>4213.544659677356</v>
+        <v>4272.890359109432</v>
       </c>
       <c r="G73">
         <v>271</v>
@@ -7395,37 +7395,37 @@
         <v>187.31</v>
       </c>
       <c r="M73">
-        <v>846.0797676632131</v>
+        <v>857.996384109174</v>
       </c>
       <c r="N73">
-        <v>-658.7697676632131</v>
+        <v>-670.686384109174</v>
       </c>
       <c r="O73">
-        <v>-151.517046562539</v>
+        <v>-154.25786834511</v>
       </c>
       <c r="P73">
-        <v>-507.2527211006741</v>
+        <v>-516.4285157640639</v>
       </c>
       <c r="Q73">
-        <v>-260.2527211006741</v>
+        <v>-269.4285157640639</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4015091098986838</v>
+        <v>0.4142130066807797</v>
       </c>
       <c r="T73">
-        <v>5.502706801079452</v>
+        <v>5.699232043975147</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.0509187214333067</v>
+        <v>0.05021151696895521</v>
       </c>
       <c r="W73">
-        <v>0.190575520736192</v>
+        <v>0.1907175273926338</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2213857453622031</v>
+        <v>0.2183109433432835</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7441,22 +7441,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2532962615933146</v>
+        <v>0.2548462615933146</v>
       </c>
       <c r="C74">
-        <v>-1095.201181432707</v>
+        <v>-1176.098896151062</v>
       </c>
       <c r="D74">
-        <v>2906.689177676726</v>
+        <v>2885.137162390445</v>
       </c>
       <c r="E74">
-        <v>4070.920415901889</v>
+        <v>4130.266115333963</v>
       </c>
       <c r="F74">
-        <v>4272.890359109432</v>
+        <v>4332.236058541507</v>
       </c>
       <c r="G74">
         <v>271</v>
@@ -7477,37 +7477,37 @@
         <v>187.31</v>
       </c>
       <c r="M74">
-        <v>857.996384109174</v>
+        <v>869.9130005551347</v>
       </c>
       <c r="N74">
-        <v>-670.686384109174</v>
+        <v>-682.6030005551347</v>
       </c>
       <c r="O74">
-        <v>-154.25786834511</v>
+        <v>-156.998690127681</v>
       </c>
       <c r="P74">
-        <v>-516.4285157640639</v>
+        <v>-525.6043104274537</v>
       </c>
       <c r="Q74">
-        <v>-269.4285157640639</v>
+        <v>-278.6043104274537</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4142130066807797</v>
+        <v>0.4278579328541419</v>
       </c>
       <c r="T74">
-        <v>5.699232043975147</v>
+        <v>5.910314712270523</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.05021151696895521</v>
+        <v>0.04952368796938048</v>
       </c>
       <c r="W74">
-        <v>0.1907175273926338</v>
+        <v>0.1908556434557484</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2183109433432835</v>
+        <v>0.2153203824755673</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7523,22 +7523,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2548462615933146</v>
+        <v>0.2563962615933146</v>
       </c>
       <c r="C75">
-        <v>-1176.098896151062</v>
+        <v>-1256.679362847626</v>
       </c>
       <c r="D75">
-        <v>2885.137162390445</v>
+        <v>2863.902395125957</v>
       </c>
       <c r="E75">
-        <v>4130.266115333963</v>
+        <v>4189.611814766039</v>
       </c>
       <c r="F75">
-        <v>4332.236058541507</v>
+        <v>4391.581757973583</v>
       </c>
       <c r="G75">
         <v>271</v>
@@ -7559,37 +7559,37 @@
         <v>187.31</v>
       </c>
       <c r="M75">
-        <v>869.9130005551347</v>
+        <v>881.8296170010955</v>
       </c>
       <c r="N75">
-        <v>-682.6030005551347</v>
+        <v>-694.5196170010954</v>
       </c>
       <c r="O75">
-        <v>-156.998690127681</v>
+        <v>-159.739511910252</v>
       </c>
       <c r="P75">
-        <v>-525.6043104274537</v>
+        <v>-534.7801050908434</v>
       </c>
       <c r="Q75">
-        <v>-278.6043104274537</v>
+        <v>-287.7801050908434</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4278579328541419</v>
+        <v>0.4425524687331474</v>
       </c>
       <c r="T75">
-        <v>5.910314712270523</v>
+        <v>6.137634508896312</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.04952368796938048</v>
+        <v>0.04885444894276723</v>
       </c>
       <c r="W75">
-        <v>0.1908556434557484</v>
+        <v>0.1909900266522923</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2153203824755673</v>
+        <v>0.2124106475772489</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7605,22 +7605,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2563962615933146</v>
+        <v>0.2579462615933147</v>
       </c>
       <c r="C76">
-        <v>-1256.679362847626</v>
+        <v>-1336.94953523108</v>
       </c>
       <c r="D76">
-        <v>2863.902395125957</v>
+        <v>2842.977922174578</v>
       </c>
       <c r="E76">
-        <v>4189.611814766039</v>
+        <v>4248.957514198114</v>
       </c>
       <c r="F76">
-        <v>4391.581757973583</v>
+        <v>4450.927457405658</v>
       </c>
       <c r="G76">
         <v>271</v>
@@ -7641,37 +7641,37 @@
         <v>187.31</v>
       </c>
       <c r="M76">
-        <v>881.8296170010955</v>
+        <v>893.7462334470562</v>
       </c>
       <c r="N76">
-        <v>-694.5196170010954</v>
+        <v>-706.4362334470561</v>
       </c>
       <c r="O76">
-        <v>-159.739511910252</v>
+        <v>-162.4803336928229</v>
       </c>
       <c r="P76">
-        <v>-534.7801050908434</v>
+        <v>-543.9558997542332</v>
       </c>
       <c r="Q76">
-        <v>-287.7801050908434</v>
+        <v>-296.9558997542332</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4425524687331474</v>
+        <v>0.4584225674824733</v>
       </c>
       <c r="T76">
-        <v>6.137634508896312</v>
+        <v>6.383139889252165</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.04885444894276723</v>
+        <v>0.04820305629019701</v>
       </c>
       <c r="W76">
-        <v>0.1909900266522923</v>
+        <v>0.1911208262969284</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2124106475772489</v>
+        <v>0.2095785056095523</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7687,22 +7687,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2579462615933147</v>
+        <v>0.2594962615933147</v>
       </c>
       <c r="C77">
-        <v>-1336.94953523108</v>
+        <v>-1416.916165261168</v>
       </c>
       <c r="D77">
-        <v>2842.977922174578</v>
+        <v>2822.356991576566</v>
       </c>
       <c r="E77">
-        <v>4248.957514198114</v>
+        <v>4308.30321363019</v>
       </c>
       <c r="F77">
-        <v>4450.927457405658</v>
+        <v>4510.273156837734</v>
       </c>
       <c r="G77">
         <v>271</v>
@@ -7723,37 +7723,37 @@
         <v>187.31</v>
       </c>
       <c r="M77">
-        <v>893.7462334470562</v>
+        <v>905.662849893017</v>
       </c>
       <c r="N77">
-        <v>-706.4362334470561</v>
+        <v>-718.352849893017</v>
       </c>
       <c r="O77">
-        <v>-162.4803336928229</v>
+        <v>-165.2211554753939</v>
       </c>
       <c r="P77">
-        <v>-543.9558997542332</v>
+        <v>-553.1316944176231</v>
       </c>
       <c r="Q77">
-        <v>-296.9558997542332</v>
+        <v>-306.1316944176231</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4584225674824733</v>
+        <v>0.4756151744609097</v>
       </c>
       <c r="T77">
-        <v>6.383139889252165</v>
+        <v>6.649104051304339</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.04820305629019701</v>
+        <v>0.04756880554953651</v>
       </c>
       <c r="W77">
-        <v>0.1911208262969284</v>
+        <v>0.1912481838456531</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2095785056095523</v>
+        <v>0.206820893693637</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7769,22 +7769,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2594962615933147</v>
+        <v>0.2610462615933147</v>
       </c>
       <c r="C78">
-        <v>-1416.916165261168</v>
+        <v>-1496.585810412724</v>
       </c>
       <c r="D78">
-        <v>2822.356991576566</v>
+        <v>2802.033045857085</v>
       </c>
       <c r="E78">
-        <v>4308.30321363019</v>
+        <v>4367.648913062265</v>
       </c>
       <c r="F78">
-        <v>4510.273156837734</v>
+        <v>4569.618856269809</v>
       </c>
       <c r="G78">
         <v>271</v>
@@ -7805,37 +7805,37 @@
         <v>187.31</v>
       </c>
       <c r="M78">
-        <v>905.662849893017</v>
+        <v>917.5794663389777</v>
       </c>
       <c r="N78">
-        <v>-718.352849893017</v>
+        <v>-730.2694663389777</v>
       </c>
       <c r="O78">
-        <v>-165.2211554753939</v>
+        <v>-167.9619772579649</v>
       </c>
       <c r="P78">
-        <v>-553.1316944176231</v>
+        <v>-562.3074890810128</v>
       </c>
       <c r="Q78">
-        <v>-306.1316944176231</v>
+        <v>-315.3074890810128</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4756151744609097</v>
+        <v>0.4943027907418189</v>
       </c>
       <c r="T78">
-        <v>6.649104051304339</v>
+        <v>6.938195531795833</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.04756880554953651</v>
+        <v>0.04695102885408799</v>
       </c>
       <c r="W78">
-        <v>0.1912481838456531</v>
+        <v>0.1913722334060991</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.206820893693637</v>
+        <v>0.2041349080612521</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7851,22 +7851,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2610462615933147</v>
+        <v>0.2625962615933146</v>
       </c>
       <c r="C79">
-        <v>-1496.585810412724</v>
+        <v>-1575.964840628084</v>
       </c>
       <c r="D79">
-        <v>2802.033045857085</v>
+        <v>2781.999715073801</v>
       </c>
       <c r="E79">
-        <v>4367.648913062265</v>
+        <v>4426.994612494341</v>
       </c>
       <c r="F79">
-        <v>4569.618856269809</v>
+        <v>4628.964555701885</v>
       </c>
       <c r="G79">
         <v>271</v>
@@ -7887,37 +7887,37 @@
         <v>187.31</v>
       </c>
       <c r="M79">
-        <v>917.5794663389777</v>
+        <v>929.4960827849385</v>
       </c>
       <c r="N79">
-        <v>-730.2694663389777</v>
+        <v>-742.1860827849384</v>
       </c>
       <c r="O79">
-        <v>-167.9619772579649</v>
+        <v>-170.7027990405358</v>
       </c>
       <c r="P79">
-        <v>-562.3074890810128</v>
+        <v>-571.4832837444026</v>
       </c>
       <c r="Q79">
-        <v>-315.3074890810128</v>
+        <v>-324.4832837444026</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4943027907418189</v>
+        <v>0.5146892812300833</v>
       </c>
       <c r="T79">
-        <v>6.938195531795833</v>
+        <v>7.25356805596837</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.04695102885408799</v>
+        <v>0.04634909258672789</v>
       </c>
       <c r="W79">
-        <v>0.1913722334060991</v>
+        <v>0.191493102208585</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2041349080612521</v>
+        <v>0.2015177938553386</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7933,22 +7933,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2625962615933146</v>
+        <v>0.2923705693066528</v>
       </c>
       <c r="C80">
-        <v>-1575.964840628084</v>
+        <v>-1971.247289559289</v>
       </c>
       <c r="D80">
-        <v>2781.999715073801</v>
+        <v>2446.062965574672</v>
       </c>
       <c r="E80">
-        <v>4426.994612494341</v>
+        <v>4486.340311926417</v>
       </c>
       <c r="F80">
-        <v>4628.964555701885</v>
+        <v>4688.310255133961</v>
       </c>
       <c r="G80">
         <v>271</v>
@@ -7969,45 +7969,45 @@
         <v>187.31</v>
       </c>
       <c r="M80">
-        <v>929.4960827849385</v>
+        <v>1105.503558160588</v>
       </c>
       <c r="N80">
-        <v>-742.1860827849384</v>
+        <v>-918.1935581605881</v>
       </c>
       <c r="O80">
-        <v>-170.7027990405358</v>
+        <v>-211.1845183769353</v>
       </c>
       <c r="P80">
-        <v>-571.4832837444026</v>
+        <v>-707.0090397836527</v>
       </c>
       <c r="Q80">
-        <v>-324.4832837444026</v>
+        <v>-460.0090397836527</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5146892812300833</v>
+        <v>0.5397521408759834</v>
       </c>
       <c r="T80">
-        <v>7.25356805596837</v>
+        <v>7.641282523745922</v>
       </c>
       <c r="U80">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04634909258672789</v>
+        <v>0.03896984291184155</v>
       </c>
       <c r="W80">
-        <v>0.191493102208585</v>
+        <v>0.2266109110413878</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.2015177938553386</v>
+        <v>0.1694340996167023</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8015,22 +8015,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2923705693066528</v>
+        <v>0.2942705693066529</v>
       </c>
       <c r="C81">
-        <v>-1971.247289559289</v>
+        <v>-2049.297496521413</v>
       </c>
       <c r="D81">
-        <v>2446.062965574672</v>
+        <v>2427.358458044623</v>
       </c>
       <c r="E81">
-        <v>4486.340311926417</v>
+        <v>4545.686011358492</v>
       </c>
       <c r="F81">
-        <v>4688.310255133961</v>
+        <v>4747.655954566036</v>
       </c>
       <c r="G81">
         <v>271</v>
@@ -8051,37 +8051,37 @@
         <v>187.31</v>
       </c>
       <c r="M81">
-        <v>1105.503558160588</v>
+        <v>1119.497274086671</v>
       </c>
       <c r="N81">
-        <v>-918.1935581605881</v>
+        <v>-932.1872740866713</v>
       </c>
       <c r="O81">
-        <v>-211.1845183769353</v>
+        <v>-214.4030730399344</v>
       </c>
       <c r="P81">
-        <v>-707.0090397836527</v>
+        <v>-717.7842010467369</v>
       </c>
       <c r="Q81">
-        <v>-460.0090397836527</v>
+        <v>-470.7842010467369</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5397521408759834</v>
+        <v>0.5644497479197826</v>
       </c>
       <c r="T81">
-        <v>7.641282523745922</v>
+        <v>8.023346649933218</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03896984291184155</v>
+        <v>0.03848271987544354</v>
       </c>
       <c r="W81">
-        <v>0.2266109110413878</v>
+        <v>0.2267257746533704</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1694340996167023</v>
+        <v>0.1673161733714935</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8097,22 +8097,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2942705693066529</v>
+        <v>0.2961705693066529</v>
       </c>
       <c r="C82">
-        <v>-2049.297496521413</v>
+        <v>-2127.063815769375</v>
       </c>
       <c r="D82">
-        <v>2427.358458044623</v>
+        <v>2408.937838228737</v>
       </c>
       <c r="E82">
-        <v>4545.686011358492</v>
+        <v>4605.031710790568</v>
       </c>
       <c r="F82">
-        <v>4747.655954566036</v>
+        <v>4807.001653998112</v>
       </c>
       <c r="G82">
         <v>271</v>
@@ -8133,37 +8133,37 @@
         <v>187.31</v>
       </c>
       <c r="M82">
-        <v>1119.497274086671</v>
+        <v>1133.490990012755</v>
       </c>
       <c r="N82">
-        <v>-932.1872740866713</v>
+        <v>-946.1809900127548</v>
       </c>
       <c r="O82">
-        <v>-214.4030730399344</v>
+        <v>-217.6216277029336</v>
       </c>
       <c r="P82">
-        <v>-717.7842010467369</v>
+        <v>-728.5593623098212</v>
       </c>
       <c r="Q82">
-        <v>-470.7842010467369</v>
+        <v>-481.5593623098212</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5644497479197826</v>
+        <v>0.5917471030734555</v>
       </c>
       <c r="T82">
-        <v>8.023346649933218</v>
+        <v>8.445628052561283</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03848271987544354</v>
+        <v>0.03800762456833929</v>
       </c>
       <c r="W82">
-        <v>0.2267257746533704</v>
+        <v>0.2268378021267856</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1673161733714935</v>
+        <v>0.1652505416014751</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8179,22 +8179,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2961705693066529</v>
+        <v>0.2980705693066529</v>
       </c>
       <c r="C83">
-        <v>-2127.063815769375</v>
+        <v>-2204.552661685854</v>
       </c>
       <c r="D83">
-        <v>2408.937838228737</v>
+        <v>2390.794691744332</v>
       </c>
       <c r="E83">
-        <v>4605.031710790568</v>
+        <v>4664.377410222643</v>
       </c>
       <c r="F83">
-        <v>4807.001653998112</v>
+        <v>4866.347353430187</v>
       </c>
       <c r="G83">
         <v>271</v>
@@ -8215,37 +8215,37 @@
         <v>187.31</v>
       </c>
       <c r="M83">
-        <v>1133.490990012755</v>
+        <v>1147.484705938838</v>
       </c>
       <c r="N83">
-        <v>-946.1809900127548</v>
+        <v>-960.1747059388381</v>
       </c>
       <c r="O83">
-        <v>-217.6216277029336</v>
+        <v>-220.8401823659328</v>
       </c>
       <c r="P83">
-        <v>-728.5593623098212</v>
+        <v>-739.3345235729053</v>
       </c>
       <c r="Q83">
-        <v>-481.5593623098212</v>
+        <v>-492.3345235729053</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5917471030734555</v>
+        <v>0.6220774976886475</v>
       </c>
       <c r="T83">
-        <v>8.445628052561283</v>
+        <v>8.914829611036911</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03800762456833929</v>
+        <v>0.03754411695165223</v>
       </c>
       <c r="W83">
-        <v>0.2268378021267856</v>
+        <v>0.2269470972228004</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1652505416014751</v>
+        <v>0.16323529109414</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8261,22 +8261,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2980705693066529</v>
+        <v>0.2999705693066529</v>
       </c>
       <c r="C84">
-        <v>-2204.552661685854</v>
+        <v>-2281.770256855921</v>
       </c>
       <c r="D84">
-        <v>2390.794691744332</v>
+        <v>2372.922796006342</v>
       </c>
       <c r="E84">
-        <v>4664.377410222643</v>
+        <v>4723.723109654718</v>
       </c>
       <c r="F84">
-        <v>4866.347353430187</v>
+        <v>4925.693052862262</v>
       </c>
       <c r="G84">
         <v>271</v>
@@ -8297,37 +8297,37 @@
         <v>187.31</v>
       </c>
       <c r="M84">
-        <v>1147.484705938838</v>
+        <v>1161.478421864922</v>
       </c>
       <c r="N84">
-        <v>-960.1747059388381</v>
+        <v>-974.1684218649216</v>
       </c>
       <c r="O84">
-        <v>-220.8401823659328</v>
+        <v>-224.058737028932</v>
       </c>
       <c r="P84">
-        <v>-739.3345235729053</v>
+        <v>-750.1096848359896</v>
       </c>
       <c r="Q84">
-        <v>-492.3345235729053</v>
+        <v>-503.1096848359896</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6220774976886475</v>
+        <v>0.6559761740232739</v>
       </c>
       <c r="T84">
-        <v>8.914829611036911</v>
+        <v>9.439231352862612</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03754411695165223</v>
+        <v>0.03709177819319858</v>
       </c>
       <c r="W84">
-        <v>0.2269470972228004</v>
+        <v>0.2270537587020438</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.16323529109414</v>
+        <v>0.1612686008399938</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8343,22 +8343,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2999705693066529</v>
+        <v>0.3018705693066528</v>
       </c>
       <c r="C85">
-        <v>-2281.770256855921</v>
+        <v>-2358.722639182557</v>
       </c>
       <c r="D85">
-        <v>2372.922796006342</v>
+        <v>2355.31611311178</v>
       </c>
       <c r="E85">
-        <v>4723.723109654718</v>
+        <v>4783.068809086793</v>
       </c>
       <c r="F85">
-        <v>4925.693052862262</v>
+        <v>4985.038752294337</v>
       </c>
       <c r="G85">
         <v>271</v>
@@ -8379,37 +8379,37 @@
         <v>187.31</v>
       </c>
       <c r="M85">
-        <v>1161.478421864922</v>
+        <v>1175.472137791005</v>
       </c>
       <c r="N85">
-        <v>-974.1684218649216</v>
+        <v>-988.1621377910049</v>
       </c>
       <c r="O85">
-        <v>-224.058737028932</v>
+        <v>-227.2772916919311</v>
       </c>
       <c r="P85">
-        <v>-750.1096848359896</v>
+        <v>-760.8848460990737</v>
       </c>
       <c r="Q85">
-        <v>-503.1096848359896</v>
+        <v>-513.8848460990737</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6559761740232739</v>
+        <v>0.6941121848997286</v>
       </c>
       <c r="T85">
-        <v>9.439231352862612</v>
+        <v>10.02918331241653</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03709177819319858</v>
+        <v>0.03665020940518432</v>
       </c>
       <c r="W85">
-        <v>0.2270537587020438</v>
+        <v>0.2271578806222575</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1612686008399938</v>
+        <v>0.1593487365442796</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8425,22 +8425,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3018705693066528</v>
+        <v>0.3037705693066529</v>
       </c>
       <c r="C86">
-        <v>-2358.722639182557</v>
+        <v>-2435.415668687749</v>
       </c>
       <c r="D86">
-        <v>2355.31611311178</v>
+        <v>2337.968783038663</v>
       </c>
       <c r="E86">
-        <v>4783.068809086793</v>
+        <v>4842.414508518868</v>
       </c>
       <c r="F86">
-        <v>4985.038752294337</v>
+        <v>5044.384451726412</v>
       </c>
       <c r="G86">
         <v>271</v>
@@ -8461,37 +8461,37 @@
         <v>187.31</v>
       </c>
       <c r="M86">
-        <v>1175.472137791005</v>
+        <v>1189.465853717088</v>
       </c>
       <c r="N86">
-        <v>-988.1621377910049</v>
+        <v>-1002.155853717088</v>
       </c>
       <c r="O86">
-        <v>-227.2772916919311</v>
+        <v>-230.4958463549303</v>
       </c>
       <c r="P86">
-        <v>-760.8848460990737</v>
+        <v>-771.6600073621578</v>
       </c>
       <c r="Q86">
-        <v>-513.8848460990737</v>
+        <v>-524.6600073621578</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6941121848997281</v>
+        <v>0.7373329972263768</v>
       </c>
       <c r="T86">
-        <v>10.02918331241652</v>
+        <v>10.69779553324429</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03665020940518432</v>
+        <v>0.03621903047100569</v>
       </c>
       <c r="W86">
-        <v>0.2271578806222575</v>
+        <v>0.2272595526149369</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1593487365442796</v>
+        <v>0.1574740455261117</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8507,22 +8507,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3037705693066529</v>
+        <v>0.3056705693066529</v>
       </c>
       <c r="C87">
-        <v>-2435.415668687749</v>
+        <v>-2511.855034015218</v>
       </c>
       <c r="D87">
-        <v>2337.968783038663</v>
+        <v>2320.87511714327</v>
       </c>
       <c r="E87">
-        <v>4842.414508518868</v>
+        <v>4901.760207950944</v>
       </c>
       <c r="F87">
-        <v>5044.384451726412</v>
+        <v>5103.730151158488</v>
       </c>
       <c r="G87">
         <v>271</v>
@@ -8543,37 +8543,37 @@
         <v>187.31</v>
       </c>
       <c r="M87">
-        <v>1189.465853717088</v>
+        <v>1203.459569643172</v>
       </c>
       <c r="N87">
-        <v>-1002.155853717088</v>
+        <v>-1016.149569643172</v>
       </c>
       <c r="O87">
-        <v>-230.4958463549303</v>
+        <v>-233.7144010179295</v>
       </c>
       <c r="P87">
-        <v>-771.6600073621578</v>
+        <v>-782.4351686252421</v>
       </c>
       <c r="Q87">
-        <v>-524.6600073621578</v>
+        <v>-535.4351686252421</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7373329972263768</v>
+        <v>0.7867282113139751</v>
       </c>
       <c r="T87">
-        <v>10.69779553324429</v>
+        <v>11.46192378561888</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03621903047100569</v>
+        <v>0.03579787895390096</v>
       </c>
       <c r="W87">
-        <v>0.2272595526149369</v>
+        <v>0.2273588601426701</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1574740455261117</v>
+        <v>0.1556429519734824</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8589,22 +8589,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3056705693066529</v>
+        <v>0.3075705693066528</v>
       </c>
       <c r="C88">
-        <v>-2511.855034015218</v>
+        <v>-2588.046258649961</v>
       </c>
       <c r="D88">
-        <v>2320.87511714327</v>
+        <v>2304.029591940602</v>
       </c>
       <c r="E88">
-        <v>4901.760207950944</v>
+        <v>4961.105907383019</v>
       </c>
       <c r="F88">
-        <v>5103.730151158488</v>
+        <v>5163.075850590563</v>
       </c>
       <c r="G88">
         <v>271</v>
@@ -8625,37 +8625,37 @@
         <v>187.31</v>
       </c>
       <c r="M88">
-        <v>1203.459569643172</v>
+        <v>1217.453285569255</v>
       </c>
       <c r="N88">
-        <v>-1016.149569643172</v>
+        <v>-1030.143285569255</v>
       </c>
       <c r="O88">
-        <v>-233.7144010179295</v>
+        <v>-236.9329556809286</v>
       </c>
       <c r="P88">
-        <v>-782.4351686252421</v>
+        <v>-793.2103298883262</v>
       </c>
       <c r="Q88">
-        <v>-535.4351686252421</v>
+        <v>-546.2103298883262</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7867282113139751</v>
+        <v>0.8437226891073577</v>
       </c>
       <c r="T88">
-        <v>11.46192378561888</v>
+        <v>12.34361023066648</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03579787895390096</v>
+        <v>0.03538640908086763</v>
       </c>
       <c r="W88">
-        <v>0.2273588601426701</v>
+        <v>0.2274558847387314</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1556429519734824</v>
+        <v>0.1538539525255114</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8671,22 +8671,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3075705693066528</v>
+        <v>0.3094705693066528</v>
       </c>
       <c r="C89">
-        <v>-2588.046258649961</v>
+        <v>-2663.994706868898</v>
       </c>
       <c r="D89">
-        <v>2304.029591940602</v>
+        <v>2287.426843153741</v>
       </c>
       <c r="E89">
-        <v>4961.105907383019</v>
+        <v>5020.451606815095</v>
       </c>
       <c r="F89">
-        <v>5163.075850590563</v>
+        <v>5222.421550022639</v>
       </c>
       <c r="G89">
         <v>271</v>
@@ -8707,37 +8707,37 @@
         <v>187.31</v>
       </c>
       <c r="M89">
-        <v>1217.453285569255</v>
+        <v>1231.447001495338</v>
       </c>
       <c r="N89">
-        <v>-1030.143285569255</v>
+        <v>-1044.137001495338</v>
       </c>
       <c r="O89">
-        <v>-236.9329556809286</v>
+        <v>-240.1515103439278</v>
       </c>
       <c r="P89">
-        <v>-793.2103298883262</v>
+        <v>-803.9854911514105</v>
       </c>
       <c r="Q89">
-        <v>-546.2103298883262</v>
+        <v>-556.9854911514105</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8437226891073577</v>
+        <v>0.9102162465329711</v>
       </c>
       <c r="T89">
-        <v>12.34361023066648</v>
+        <v>13.37224441655536</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03538640908086763</v>
+        <v>0.03498429079585776</v>
       </c>
       <c r="W89">
-        <v>0.2274558847387314</v>
+        <v>0.2275507042303367</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1538539525255114</v>
+        <v>0.1521056121559032</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8753,22 +8753,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3094705693066528</v>
+        <v>0.3113705693066529</v>
       </c>
       <c r="C90">
-        <v>-2663.994706868898</v>
+        <v>-2739.705589436059</v>
       </c>
       <c r="D90">
-        <v>2287.426843153741</v>
+        <v>2271.061660018655</v>
       </c>
       <c r="E90">
-        <v>5020.451606815095</v>
+        <v>5079.79730624717</v>
       </c>
       <c r="F90">
-        <v>5222.421550022639</v>
+        <v>5281.767249454714</v>
       </c>
       <c r="G90">
         <v>271</v>
@@ -8789,37 +8789,37 @@
         <v>187.31</v>
       </c>
       <c r="M90">
-        <v>1231.447001495338</v>
+        <v>1245.440717421422</v>
       </c>
       <c r="N90">
-        <v>-1044.137001495338</v>
+        <v>-1058.130717421422</v>
       </c>
       <c r="O90">
-        <v>-240.1515103439278</v>
+        <v>-243.370065006927</v>
       </c>
       <c r="P90">
-        <v>-803.9854911514105</v>
+        <v>-814.7606524144946</v>
       </c>
       <c r="Q90">
-        <v>-556.9854911514105</v>
+        <v>-567.7606524144946</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.9102162465329711</v>
+        <v>0.9887995416723319</v>
       </c>
       <c r="T90">
-        <v>13.37224441655536</v>
+        <v>14.58790299987857</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03498429079585776</v>
+        <v>0.03459120887680318</v>
       </c>
       <c r="W90">
-        <v>0.2275507042303367</v>
+        <v>0.2276433929468498</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1521056121559032</v>
+        <v>0.1503965603339268</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8835,22 +8835,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3113705693066529</v>
+        <v>0.3132705693066529</v>
       </c>
       <c r="C91">
-        <v>-2739.705589436059</v>
+        <v>-2815.183969055046</v>
       </c>
       <c r="D91">
-        <v>2271.061660018655</v>
+        <v>2254.928979831744</v>
       </c>
       <c r="E91">
-        <v>5079.79730624717</v>
+        <v>5139.143005679246</v>
       </c>
       <c r="F91">
-        <v>5281.767249454714</v>
+        <v>5341.11294888679</v>
       </c>
       <c r="G91">
         <v>271</v>
@@ -8871,37 +8871,37 @@
         <v>187.31</v>
       </c>
       <c r="M91">
-        <v>1245.440717421422</v>
+        <v>1259.434433347505</v>
       </c>
       <c r="N91">
-        <v>-1058.130717421422</v>
+        <v>-1072.124433347505</v>
       </c>
       <c r="O91">
-        <v>-243.370065006927</v>
+        <v>-246.5886196699262</v>
       </c>
       <c r="P91">
-        <v>-814.7606524144946</v>
+        <v>-825.535813677579</v>
       </c>
       <c r="Q91">
-        <v>-567.7606524144946</v>
+        <v>-578.535813677579</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9887995416723319</v>
+        <v>1.083099495839565</v>
       </c>
       <c r="T91">
-        <v>14.58790299987857</v>
+        <v>16.04669329986644</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03459120887680318</v>
+        <v>0.03420686211150537</v>
       </c>
       <c r="W91">
-        <v>0.2276433929468498</v>
+        <v>0.227734021914107</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1503965603339268</v>
+        <v>0.1487254874413276</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8917,22 +8917,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3132705693066529</v>
+        <v>0.3151705693066529</v>
       </c>
       <c r="C92">
-        <v>-2815.183969055046</v>
+        <v>-2890.434765590745</v>
       </c>
       <c r="D92">
-        <v>2254.928979831744</v>
+        <v>2239.023882728121</v>
       </c>
       <c r="E92">
-        <v>5139.143005679246</v>
+        <v>5198.488705111322</v>
       </c>
       <c r="F92">
-        <v>5341.11294888679</v>
+        <v>5400.458648318866</v>
       </c>
       <c r="G92">
         <v>271</v>
@@ -8953,37 +8953,37 @@
         <v>187.31</v>
       </c>
       <c r="M92">
-        <v>1259.434433347505</v>
+        <v>1273.428149273589</v>
       </c>
       <c r="N92">
-        <v>-1072.124433347505</v>
+        <v>-1086.118149273589</v>
       </c>
       <c r="O92">
-        <v>-246.5886196699262</v>
+        <v>-249.8071743329254</v>
       </c>
       <c r="P92">
-        <v>-825.535813677579</v>
+        <v>-836.3109749406633</v>
       </c>
       <c r="Q92">
-        <v>-578.535813677579</v>
+        <v>-589.3109749406633</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.083099495839565</v>
+        <v>1.198354995377295</v>
       </c>
       <c r="T92">
-        <v>16.04669329986644</v>
+        <v>17.82965922207382</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03420686211150537</v>
+        <v>0.03383096252786245</v>
       </c>
       <c r="W92">
-        <v>0.227734021914107</v>
+        <v>0.22782265903593</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1487254874413276</v>
+        <v>0.1470911414254888</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8999,22 +8999,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3151705693066529</v>
+        <v>0.3170705693066529</v>
       </c>
       <c r="C93">
-        <v>-2890.434765590745</v>
+        <v>-2965.462761071583</v>
       </c>
       <c r="D93">
-        <v>2239.023882728121</v>
+        <v>2223.341586679358</v>
       </c>
       <c r="E93">
-        <v>5198.488705111322</v>
+        <v>5257.834404543397</v>
       </c>
       <c r="F93">
-        <v>5400.458648318866</v>
+        <v>5459.804347750941</v>
       </c>
       <c r="G93">
         <v>271</v>
@@ -9035,37 +9035,37 @@
         <v>187.31</v>
       </c>
       <c r="M93">
-        <v>1273.428149273589</v>
+        <v>1287.421865199672</v>
       </c>
       <c r="N93">
-        <v>-1086.118149273589</v>
+        <v>-1100.111865199672</v>
       </c>
       <c r="O93">
-        <v>-249.8071743329254</v>
+        <v>-253.0257289959245</v>
       </c>
       <c r="P93">
-        <v>-836.3109749406633</v>
+        <v>-847.0861362037474</v>
       </c>
       <c r="Q93">
-        <v>-589.3109749406633</v>
+        <v>-600.0861362037474</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.198354995377295</v>
+        <v>1.342424369799458</v>
       </c>
       <c r="T93">
-        <v>17.82965922207382</v>
+        <v>20.05836662483306</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03383096252786245</v>
+        <v>0.03346323467429873</v>
       </c>
       <c r="W93">
-        <v>0.22782265903593</v>
+        <v>0.2279093692638004</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1470911414254888</v>
+        <v>0.145492324670864</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9081,22 +9081,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3170705693066529</v>
+        <v>0.3189705693066529</v>
       </c>
       <c r="C94">
-        <v>-2965.462761071583</v>
+        <v>-3040.272604483052</v>
       </c>
       <c r="D94">
-        <v>2223.341586679358</v>
+        <v>2207.877442699965</v>
       </c>
       <c r="E94">
-        <v>5257.834404543397</v>
+        <v>5317.180103975473</v>
       </c>
       <c r="F94">
-        <v>5459.804347750941</v>
+        <v>5519.150047183017</v>
       </c>
       <c r="G94">
         <v>271</v>
@@ -9117,37 +9117,37 @@
         <v>187.31</v>
       </c>
       <c r="M94">
-        <v>1287.421865199672</v>
+        <v>1301.415581125755</v>
       </c>
       <c r="N94">
-        <v>-1100.111865199672</v>
+        <v>-1114.105581125755</v>
       </c>
       <c r="O94">
-        <v>-253.0257289959245</v>
+        <v>-256.2442836589237</v>
       </c>
       <c r="P94">
-        <v>-847.0861362037474</v>
+        <v>-857.8612974668317</v>
       </c>
       <c r="Q94">
-        <v>-600.0861362037474</v>
+        <v>-610.8612974668317</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.342424369799458</v>
+        <v>1.527656422627951</v>
       </c>
       <c r="T94">
-        <v>20.05836662483306</v>
+        <v>22.92384757123778</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03346323467429873</v>
+        <v>0.03310341494661809</v>
       </c>
       <c r="W94">
-        <v>0.2279093692638004</v>
+        <v>0.2279942147555875</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.145492324670864</v>
+        <v>0.1439278910722526</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9163,22 +9163,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3189705693066529</v>
+        <v>0.3208705693066529</v>
       </c>
       <c r="C95">
-        <v>-3040.272604483052</v>
+        <v>-3114.868816362546</v>
       </c>
       <c r="D95">
-        <v>2207.877442699965</v>
+        <v>2192.626930252546</v>
       </c>
       <c r="E95">
-        <v>5317.180103975473</v>
+        <v>5376.525803407548</v>
       </c>
       <c r="F95">
-        <v>5519.150047183017</v>
+        <v>5578.495746615092</v>
       </c>
       <c r="G95">
         <v>271</v>
@@ -9199,37 +9199,37 @@
         <v>187.31</v>
       </c>
       <c r="M95">
-        <v>1301.415581125755</v>
+        <v>1315.409297051839</v>
       </c>
       <c r="N95">
-        <v>-1114.105581125755</v>
+        <v>-1128.099297051839</v>
       </c>
       <c r="O95">
-        <v>-256.2442836589237</v>
+        <v>-259.4628383219229</v>
       </c>
       <c r="P95">
-        <v>-857.8612974668317</v>
+        <v>-868.6364587299158</v>
       </c>
       <c r="Q95">
-        <v>-610.8612974668317</v>
+        <v>-621.6364587299158</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.527656422627951</v>
+        <v>1.774632493065944</v>
       </c>
       <c r="T95">
-        <v>22.92384757123778</v>
+        <v>26.74448883311075</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03310341494661809</v>
+        <v>0.03275125095782429</v>
       </c>
       <c r="W95">
-        <v>0.2279942147555875</v>
+        <v>0.2280772550241451</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1439278910722526</v>
+        <v>0.1423967432948882</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9245,22 +9245,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3208705693066529</v>
+        <v>0.3227705693066529</v>
       </c>
       <c r="C96">
-        <v>-3114.868816362546</v>
+        <v>-3189.255793205102</v>
       </c>
       <c r="D96">
-        <v>2192.626930252546</v>
+        <v>2177.585652842066</v>
       </c>
       <c r="E96">
-        <v>5376.525803407548</v>
+        <v>5435.871502839624</v>
       </c>
       <c r="F96">
-        <v>5578.495746615092</v>
+        <v>5637.841446047168</v>
       </c>
       <c r="G96">
         <v>271</v>
@@ -9281,37 +9281,37 @@
         <v>187.31</v>
       </c>
       <c r="M96">
-        <v>1315.409297051839</v>
+        <v>1329.403012977922</v>
       </c>
       <c r="N96">
-        <v>-1128.099297051839</v>
+        <v>-1142.093012977922</v>
       </c>
       <c r="O96">
-        <v>-259.4628383219229</v>
+        <v>-262.6813929849221</v>
       </c>
       <c r="P96">
-        <v>-868.6364587299158</v>
+        <v>-879.411619993</v>
       </c>
       <c r="Q96">
-        <v>-621.6364587299158</v>
+        <v>-632.411619993</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.774632493065944</v>
+        <v>2.120398991679134</v>
       </c>
       <c r="T96">
-        <v>26.74448883311075</v>
+        <v>32.09338659973292</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03275125095782429</v>
+        <v>0.03240650094774192</v>
       </c>
       <c r="W96">
-        <v>0.2280772550241451</v>
+        <v>0.2281585470765225</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1423967432948882</v>
+        <v>0.1408978302075735</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9327,22 +9327,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3227705693066529</v>
+        <v>0.3246705693066528</v>
       </c>
       <c r="C97">
-        <v>-3189.255793205102</v>
+        <v>-3263.43781168901</v>
       </c>
       <c r="D97">
-        <v>2177.585652842066</v>
+        <v>2162.749333790233</v>
       </c>
       <c r="E97">
-        <v>5435.871502839624</v>
+        <v>5495.217202271699</v>
       </c>
       <c r="F97">
-        <v>5637.841446047168</v>
+        <v>5697.187145479243</v>
       </c>
       <c r="G97">
         <v>271</v>
@@ -9363,37 +9363,37 @@
         <v>187.31</v>
       </c>
       <c r="M97">
-        <v>1329.403012977922</v>
+        <v>1343.396728904005</v>
       </c>
       <c r="N97">
-        <v>-1142.093012977922</v>
+        <v>-1156.086728904005</v>
       </c>
       <c r="O97">
-        <v>-262.6813929849221</v>
+        <v>-265.8999476479212</v>
       </c>
       <c r="P97">
-        <v>-879.411619993</v>
+        <v>-890.1867812560843</v>
       </c>
       <c r="Q97">
-        <v>-632.411619993</v>
+        <v>-643.1867812560843</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.120398991679134</v>
+        <v>2.639048739598918</v>
       </c>
       <c r="T97">
-        <v>32.09338659973292</v>
+        <v>40.11673324966615</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03240650094774192</v>
+        <v>0.03206893322953628</v>
       </c>
       <c r="W97">
-        <v>0.2281585470765225</v>
+        <v>0.2282381455444754</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1408978302075735</v>
+        <v>0.1394301444762447</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9409,22 +9409,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3246705693066529</v>
+        <v>0.3265705693066528</v>
       </c>
       <c r="C98">
-        <v>-3263.43781168901</v>
+        <v>-3337.419032729881</v>
       </c>
       <c r="D98">
-        <v>2162.749333790232</v>
+        <v>2148.113812181437</v>
       </c>
       <c r="E98">
-        <v>5495.217202271699</v>
+        <v>5554.562901703774</v>
       </c>
       <c r="F98">
-        <v>5697.187145479243</v>
+        <v>5756.532844911318</v>
       </c>
       <c r="G98">
         <v>271</v>
@@ -9445,37 +9445,37 @@
         <v>187.31</v>
       </c>
       <c r="M98">
-        <v>1343.396728904005</v>
+        <v>1357.390444830089</v>
       </c>
       <c r="N98">
-        <v>-1156.086728904005</v>
+        <v>-1170.080444830089</v>
       </c>
       <c r="O98">
-        <v>-265.8999476479212</v>
+        <v>-269.1185023109204</v>
       </c>
       <c r="P98">
-        <v>-890.1867812560843</v>
+        <v>-900.9619425191684</v>
       </c>
       <c r="Q98">
-        <v>-643.1867812560843</v>
+        <v>-653.9619425191684</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.639048739598911</v>
+        <v>3.503464986131881</v>
       </c>
       <c r="T98">
-        <v>40.11673324966605</v>
+        <v>53.4889776662214</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03206893322953628</v>
+        <v>0.0317383256704689</v>
       </c>
       <c r="W98">
-        <v>0.2282381455444754</v>
+        <v>0.2283161028069035</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1394301444762447</v>
+        <v>0.1379927203063864</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9491,22 +9491,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3265705693066528</v>
+        <v>0.3284705693066529</v>
       </c>
       <c r="C99">
-        <v>-3337.419032729881</v>
+        <v>-3411.203505371194</v>
       </c>
       <c r="D99">
-        <v>2148.113812181437</v>
+        <v>2133.6750389722</v>
       </c>
       <c r="E99">
-        <v>5554.562901703774</v>
+        <v>5613.908601135849</v>
       </c>
       <c r="F99">
-        <v>5756.532844911318</v>
+        <v>5815.878544343394</v>
       </c>
       <c r="G99">
         <v>271</v>
@@ -9527,37 +9527,37 @@
         <v>187.31</v>
       </c>
       <c r="M99">
-        <v>1357.390444830089</v>
+        <v>1371.384160756172</v>
       </c>
       <c r="N99">
-        <v>-1170.080444830089</v>
+        <v>-1184.074160756172</v>
       </c>
       <c r="O99">
-        <v>-269.1185023109204</v>
+        <v>-272.3370569739196</v>
       </c>
       <c r="P99">
-        <v>-900.9619425191684</v>
+        <v>-911.7371037822526</v>
       </c>
       <c r="Q99">
-        <v>-653.9619425191684</v>
+        <v>-664.7371037822526</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.503464986131881</v>
+        <v>5.232297479197823</v>
       </c>
       <c r="T99">
-        <v>53.4889776662214</v>
+        <v>80.23346649933211</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0317383256704689</v>
+        <v>0.0314144652044437</v>
       </c>
       <c r="W99">
-        <v>0.2283161028069035</v>
+        <v>0.2283924691047922</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1379927203063864</v>
+        <v>0.1365846313236683</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9573,22 +9573,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3284705693066529</v>
+        <v>0.3303705693066529</v>
       </c>
       <c r="C100">
-        <v>-3411.203505371194</v>
+        <v>-3484.795170518994</v>
       </c>
       <c r="D100">
-        <v>2133.6750389722</v>
+        <v>2119.429073256474</v>
       </c>
       <c r="E100">
-        <v>5613.908601135849</v>
+        <v>5673.254300567924</v>
       </c>
       <c r="F100">
-        <v>5815.878544343394</v>
+        <v>5875.224243775468</v>
       </c>
       <c r="G100">
         <v>271</v>
@@ -9609,37 +9609,37 @@
         <v>187.31</v>
       </c>
       <c r="M100">
-        <v>1371.384160756172</v>
+        <v>1385.377876682255</v>
       </c>
       <c r="N100">
-        <v>-1184.074160756172</v>
+        <v>-1198.067876682255</v>
       </c>
       <c r="O100">
-        <v>-272.3370569739196</v>
+        <v>-275.5556116369188</v>
       </c>
       <c r="P100">
-        <v>-911.7371037822526</v>
+        <v>-922.5122650453367</v>
       </c>
       <c r="Q100">
-        <v>-664.7371037822526</v>
+        <v>-675.5122650453367</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.232297479197823</v>
+        <v>10.41879495839565</v>
       </c>
       <c r="T100">
-        <v>80.23346649933211</v>
+        <v>160.4669329986642</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0314144652044437</v>
+        <v>0.03109714737409579</v>
       </c>
       <c r="W100">
-        <v>0.2283924691047922</v>
+        <v>0.2284672926491882</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9647,91 +9647,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1365846313236683</v>
+        <v>0.1352049885830251</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3303705693066529</v>
-      </c>
-      <c r="C101">
-        <v>-3484.795170518994</v>
-      </c>
-      <c r="D101">
-        <v>2119.429073256474</v>
-      </c>
-      <c r="E101">
-        <v>5673.254300567924</v>
-      </c>
-      <c r="F101">
-        <v>5875.224243775468</v>
-      </c>
-      <c r="G101">
-        <v>271</v>
-      </c>
-      <c r="H101">
-        <v>5732.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>434.31</v>
-      </c>
-      <c r="K101">
-        <v>247</v>
-      </c>
-      <c r="L101">
-        <v>187.31</v>
-      </c>
-      <c r="M101">
-        <v>1385.377876682255</v>
-      </c>
-      <c r="N101">
-        <v>-1198.067876682255</v>
-      </c>
-      <c r="O101">
-        <v>-275.5556116369188</v>
-      </c>
-      <c r="P101">
-        <v>-922.5122650453367</v>
-      </c>
-      <c r="Q101">
-        <v>-675.5122650453367</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>10.41879495839565</v>
-      </c>
-      <c r="T101">
-        <v>160.4669329986642</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03109714737409579</v>
-      </c>
-      <c r="W101">
-        <v>0.2284672926491882</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1352049885830251</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
